--- a/matlab/POLAR_SR_HR/node_struct.xlsx
+++ b/matlab/POLAR_SR_HR/node_struct.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\dev\polar_dev\matlab\POLAR_SR_HR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22BF8576-7931-43C8-B95D-E79D8736E751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86355DDB-9055-461F-84C8-F088DA6D7886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2700" yWindow="2580" windowWidth="23040" windowHeight="12108" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="1|2" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="1|4" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -480,6 +481,10 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" t="str">
+        <f>IF(ISNUMBER(VLOOKUP(A1, $E:$E, 1, FALSE)), 1, "")</f>
+        <v/>
+      </c>
       <c r="E1" t="s">
         <v>0</v>
       </c>
@@ -526,6 +531,10 @@
       </c>
       <c r="C2">
         <v>-1</v>
+      </c>
+      <c r="D2">
+        <f>IF(ISNUMBER(VLOOKUP(A2, $E:$E, 1, FALSE)), 1, "")</f>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -583,6 +592,10 @@
       <c r="C3">
         <v>-1</v>
       </c>
+      <c r="D3" t="str">
+        <f t="shared" ref="D2:D67" si="0">IF(ISNUMBER(VLOOKUP(A3, $E:$E, 1, FALSE)), 1, "")</f>
+        <v/>
+      </c>
       <c r="E3">
         <v>513</v>
       </c>
@@ -639,6 +652,10 @@
       <c r="C4">
         <v>-1</v>
       </c>
+      <c r="D4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E4">
         <v>769</v>
       </c>
@@ -695,6 +712,10 @@
       <c r="C5">
         <v>-1</v>
       </c>
+      <c r="D5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E5">
         <v>833</v>
       </c>
@@ -751,6 +772,10 @@
       <c r="C6">
         <v>-1</v>
       </c>
+      <c r="D6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E6">
         <v>865</v>
       </c>
@@ -807,6 +832,10 @@
       <c r="C7">
         <v>-1</v>
       </c>
+      <c r="D7" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E7">
         <v>881</v>
       </c>
@@ -866,6 +895,10 @@
       <c r="C8">
         <v>2</v>
       </c>
+      <c r="D8" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E8">
         <v>889</v>
       </c>
@@ -925,6 +958,10 @@
       <c r="C9">
         <v>3</v>
       </c>
+      <c r="D9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E9">
         <v>897</v>
       </c>
@@ -981,6 +1018,10 @@
       <c r="C10">
         <v>-1</v>
       </c>
+      <c r="D10">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="E10">
         <v>929</v>
       </c>
@@ -1040,6 +1081,10 @@
       <c r="C11">
         <v>-1</v>
       </c>
+      <c r="D11" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E11">
         <v>945</v>
       </c>
@@ -1099,6 +1144,10 @@
       <c r="C12">
         <v>-1</v>
       </c>
+      <c r="D12" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E12">
         <v>961</v>
       </c>
@@ -1158,6 +1207,10 @@
       <c r="C13">
         <v>2</v>
       </c>
+      <c r="D13" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E13">
         <v>977</v>
       </c>
@@ -1217,6 +1270,10 @@
       <c r="C14">
         <v>2</v>
       </c>
+      <c r="D14" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E14">
         <v>993</v>
       </c>
@@ -1273,6 +1330,10 @@
       <c r="C15">
         <v>2</v>
       </c>
+      <c r="D15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E15">
         <v>1025</v>
       </c>
@@ -1329,6 +1390,10 @@
       <c r="C16">
         <v>1</v>
       </c>
+      <c r="D16" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E16">
         <v>1153</v>
       </c>
@@ -1385,6 +1450,10 @@
       <c r="C17">
         <v>2</v>
       </c>
+      <c r="D17">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="E17">
         <v>1217</v>
       </c>
@@ -1441,6 +1510,10 @@
       <c r="C18">
         <v>2</v>
       </c>
+      <c r="D18">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="E18">
         <v>1249</v>
       </c>
@@ -1500,6 +1573,10 @@
       <c r="C19">
         <v>2</v>
       </c>
+      <c r="D19">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="E19">
         <v>1265</v>
       </c>
@@ -1559,6 +1636,10 @@
       <c r="C20">
         <v>-1</v>
       </c>
+      <c r="D20">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="E20">
         <v>1281</v>
       </c>
@@ -1615,6 +1696,10 @@
       <c r="C21">
         <v>4</v>
       </c>
+      <c r="D21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E21">
         <v>1345</v>
       </c>
@@ -1671,6 +1756,10 @@
       <c r="C22">
         <v>3</v>
       </c>
+      <c r="D22">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="E22">
         <v>1377</v>
       </c>
@@ -1730,6 +1819,10 @@
       <c r="C23">
         <v>2</v>
       </c>
+      <c r="D23">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="E23">
         <v>1393</v>
       </c>
@@ -1789,6 +1882,10 @@
       <c r="C24">
         <v>-1</v>
       </c>
+      <c r="D24">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="E24">
         <v>1409</v>
       </c>
@@ -1845,6 +1942,10 @@
       <c r="C25">
         <v>-1</v>
       </c>
+      <c r="D25" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E25">
         <v>1441</v>
       </c>
@@ -1904,6 +2005,10 @@
       <c r="C26">
         <v>3</v>
       </c>
+      <c r="D26" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E26">
         <v>1457</v>
       </c>
@@ -1963,6 +2068,10 @@
       <c r="C27">
         <v>2</v>
       </c>
+      <c r="D27">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="E27">
         <v>1473</v>
       </c>
@@ -2019,6 +2128,10 @@
       <c r="C28">
         <v>3</v>
       </c>
+      <c r="D28" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E28">
         <v>1481</v>
       </c>
@@ -2069,6 +2182,10 @@
       <c r="C29">
         <v>3</v>
       </c>
+      <c r="D29" t="str">
+        <f>IF(ISNUMBER(VLOOKUP(A29, $E:$E, 1, FALSE)), 1, "")</f>
+        <v/>
+      </c>
       <c r="E29">
         <v>1489</v>
       </c>
@@ -2116,6 +2233,10 @@
       <c r="C30">
         <v>2</v>
       </c>
+      <c r="D30">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="E30">
         <v>1505</v>
       </c>
@@ -2166,6 +2287,10 @@
       <c r="C31">
         <v>2</v>
       </c>
+      <c r="D31" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E31">
         <v>1537</v>
       </c>
@@ -2213,6 +2338,10 @@
       <c r="C32">
         <v>3</v>
       </c>
+      <c r="D32" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E32">
         <v>1601</v>
       </c>
@@ -2263,6 +2392,10 @@
       <c r="C33">
         <v>2</v>
       </c>
+      <c r="D33">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="E33">
         <v>1633</v>
       </c>
@@ -2310,6 +2443,10 @@
       <c r="C34">
         <v>3</v>
       </c>
+      <c r="D34" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E34">
         <v>1641</v>
       </c>
@@ -2360,6 +2497,10 @@
       <c r="C35">
         <v>1</v>
       </c>
+      <c r="D35" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E35">
         <v>1649</v>
       </c>
@@ -2407,6 +2548,10 @@
       <c r="C36">
         <v>2</v>
       </c>
+      <c r="D36">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="E36">
         <v>1665</v>
       </c>
@@ -2457,6 +2602,10 @@
       <c r="C37">
         <v>1</v>
       </c>
+      <c r="D37" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E37">
         <v>1681</v>
       </c>
@@ -2504,6 +2653,10 @@
       <c r="C38">
         <v>1</v>
       </c>
+      <c r="D38" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E38">
         <v>1689</v>
       </c>
@@ -2554,6 +2707,10 @@
       <c r="C39">
         <v>1</v>
       </c>
+      <c r="D39" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E39">
         <v>1697</v>
       </c>
@@ -2601,6 +2758,10 @@
       <c r="C40">
         <v>2</v>
       </c>
+      <c r="D40">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="E40">
         <v>1729</v>
       </c>
@@ -2648,6 +2809,10 @@
       <c r="C41">
         <v>2</v>
       </c>
+      <c r="D41">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="E41">
         <v>1793</v>
       </c>
@@ -2695,6 +2860,10 @@
       <c r="C42">
         <v>2</v>
       </c>
+      <c r="D42">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="E42">
         <v>1809</v>
       </c>
@@ -2745,6 +2914,10 @@
       <c r="C43">
         <v>-1</v>
       </c>
+      <c r="D43">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="E43">
         <v>1825</v>
       </c>
@@ -2792,6 +2965,10 @@
       <c r="C44">
         <v>-1</v>
       </c>
+      <c r="D44" t="str">
+        <f>IF(ISNUMBER(VLOOKUP(A44, $E:$E, 1, FALSE)), 1, "")</f>
+        <v/>
+      </c>
       <c r="E44">
         <v>1857</v>
       </c>
@@ -2842,6 +3019,10 @@
       <c r="C45">
         <v>4</v>
       </c>
+      <c r="D45" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E45">
         <v>1921</v>
       </c>
@@ -2889,6 +3070,10 @@
       <c r="C46">
         <v>2</v>
       </c>
+      <c r="D46">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="E46">
         <v>2049</v>
       </c>
@@ -2936,6 +3121,10 @@
       <c r="C47">
         <v>3</v>
       </c>
+      <c r="D47" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E47">
         <v>2177</v>
       </c>
@@ -2986,6 +3175,10 @@
       <c r="C48">
         <v>3</v>
       </c>
+      <c r="D48" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E48">
         <v>2241</v>
       </c>
@@ -3033,6 +3226,10 @@
       <c r="C49">
         <v>-1</v>
       </c>
+      <c r="D49">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="E49">
         <v>2273</v>
       </c>
@@ -3074,6 +3271,10 @@
       <c r="C50">
         <v>-1</v>
       </c>
+      <c r="D50" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E50">
         <v>2289</v>
       </c>
@@ -3115,6 +3316,10 @@
       <c r="C51">
         <v>-1</v>
       </c>
+      <c r="D51" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E51">
         <v>2305</v>
       </c>
@@ -3153,6 +3358,10 @@
       <c r="C52">
         <v>-1</v>
       </c>
+      <c r="D52" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E52">
         <v>2369</v>
       </c>
@@ -3191,6 +3400,10 @@
       <c r="C53">
         <v>4</v>
       </c>
+      <c r="D53" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E53">
         <v>2385</v>
       </c>
@@ -3229,6 +3442,10 @@
       <c r="C54">
         <v>-1</v>
       </c>
+      <c r="D54">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="E54">
         <v>2393</v>
       </c>
@@ -3273,6 +3490,10 @@
       <c r="C55">
         <v>-1</v>
       </c>
+      <c r="D55" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E55">
         <v>2401</v>
       </c>
@@ -3311,6 +3532,10 @@
       <c r="C56">
         <v>-1</v>
       </c>
+      <c r="D56" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E56">
         <v>2409</v>
       </c>
@@ -3355,6 +3580,10 @@
       <c r="C57">
         <v>3</v>
       </c>
+      <c r="D57" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E57">
         <v>2417</v>
       </c>
@@ -3393,6 +3622,10 @@
       <c r="C58">
         <v>2</v>
       </c>
+      <c r="D58">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="E58">
         <v>2433</v>
       </c>
@@ -3431,6 +3664,10 @@
       <c r="C59">
         <v>2</v>
       </c>
+      <c r="D59" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E59">
         <v>2449</v>
       </c>
@@ -3475,6 +3712,10 @@
       <c r="C60">
         <v>3</v>
       </c>
+      <c r="D60" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E60">
         <v>2465</v>
       </c>
@@ -3513,6 +3754,10 @@
       <c r="C61">
         <v>2</v>
       </c>
+      <c r="D61">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="E61">
         <v>2497</v>
       </c>
@@ -3551,6 +3796,10 @@
       <c r="C62">
         <v>3</v>
       </c>
+      <c r="D62" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E62">
         <v>2561</v>
       </c>
@@ -3589,6 +3838,10 @@
       <c r="C63">
         <v>1</v>
       </c>
+      <c r="D63" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E63">
         <v>2593</v>
       </c>
@@ -3630,6 +3883,10 @@
       <c r="C64">
         <v>2</v>
       </c>
+      <c r="D64">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="E64">
         <v>2609</v>
       </c>
@@ -3668,6 +3925,10 @@
       <c r="C65">
         <v>2</v>
       </c>
+      <c r="D65" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E65">
         <v>2617</v>
       </c>
@@ -3709,6 +3970,10 @@
       <c r="C66">
         <v>2</v>
       </c>
+      <c r="D66" t="str">
+        <f>IF(ISNUMBER(VLOOKUP(A66, $E:$E, 1, FALSE)), 1, "")</f>
+        <v/>
+      </c>
       <c r="E66">
         <v>2625</v>
       </c>
@@ -3747,6 +4012,10 @@
       <c r="C67">
         <v>3</v>
       </c>
+      <c r="D67" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E67">
         <v>2641</v>
       </c>
@@ -3788,6 +4057,10 @@
       <c r="C68">
         <v>2</v>
       </c>
+      <c r="D68">
+        <f t="shared" ref="D68:D91" si="1">IF(ISNUMBER(VLOOKUP(A68, $E:$E, 1, FALSE)), 1, "")</f>
+        <v>1</v>
+      </c>
       <c r="E68">
         <v>2657</v>
       </c>
@@ -3817,6 +4090,10 @@
       <c r="C69">
         <v>2</v>
       </c>
+      <c r="D69" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="E69">
         <v>2689</v>
       </c>
@@ -3849,6 +4126,10 @@
       <c r="C70">
         <v>1</v>
       </c>
+      <c r="D70" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="E70">
         <v>2705</v>
       </c>
@@ -3881,6 +4162,10 @@
       <c r="C71">
         <v>4</v>
       </c>
+      <c r="D71">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
       <c r="E71">
         <v>2721</v>
       </c>
@@ -3913,6 +4198,10 @@
       <c r="C72">
         <v>-1</v>
       </c>
+      <c r="D72">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
       <c r="E72">
         <v>2753</v>
       </c>
@@ -3942,6 +4231,10 @@
       <c r="C73">
         <v>4</v>
       </c>
+      <c r="D73" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="E73">
         <v>2817</v>
       </c>
@@ -3971,6 +4264,10 @@
       <c r="C74">
         <v>3</v>
       </c>
+      <c r="D74">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
       <c r="E74">
         <v>2833</v>
       </c>
@@ -4006,6 +4303,10 @@
       <c r="C75">
         <v>3</v>
       </c>
+      <c r="D75">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
       <c r="E75">
         <v>2849</v>
       </c>
@@ -4039,6 +4340,10 @@
       <c r="C76">
         <v>3</v>
       </c>
+      <c r="D76">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
       <c r="E76">
         <v>2881</v>
       </c>
@@ -4068,6 +4373,10 @@
       <c r="C77">
         <v>-1</v>
       </c>
+      <c r="D77">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
       <c r="E77">
         <v>2945</v>
       </c>
@@ -4097,6 +4406,10 @@
       <c r="C78">
         <v>-1</v>
       </c>
+      <c r="D78" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="E78">
         <v>3073</v>
       </c>
@@ -4126,6 +4439,10 @@
       <c r="C79">
         <v>2</v>
       </c>
+      <c r="D79" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="E79">
         <v>3105</v>
       </c>
@@ -4146,6 +4463,10 @@
       <c r="C80">
         <v>2</v>
       </c>
+      <c r="D80" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="E80">
         <v>3121</v>
       </c>
@@ -4169,6 +4490,10 @@
       <c r="C81">
         <v>3</v>
       </c>
+      <c r="D81" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="E81">
         <v>3137</v>
       </c>
@@ -4189,6 +4514,10 @@
       <c r="C82">
         <v>2</v>
       </c>
+      <c r="D82">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
       <c r="E82">
         <v>3153</v>
       </c>
@@ -4212,6 +4541,10 @@
       <c r="C83">
         <v>2</v>
       </c>
+      <c r="D83" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="E83">
         <v>3169</v>
       </c>
@@ -4232,6 +4565,10 @@
       <c r="C84">
         <v>2</v>
       </c>
+      <c r="D84" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="E84">
         <v>3201</v>
       </c>
@@ -4252,6 +4589,10 @@
       <c r="C85">
         <v>3</v>
       </c>
+      <c r="D85" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="E85">
         <v>3209</v>
       </c>
@@ -4275,6 +4616,10 @@
       <c r="C86">
         <v>2</v>
       </c>
+      <c r="D86">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
       <c r="E86">
         <v>3217</v>
       </c>
@@ -4299,6 +4644,10 @@
       <c r="C87">
         <v>4</v>
       </c>
+      <c r="D87">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
       <c r="E87">
         <v>3233</v>
       </c>
@@ -4322,6 +4671,10 @@
       <c r="C88">
         <v>3</v>
       </c>
+      <c r="D88">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
       <c r="E88">
         <v>3265</v>
       </c>
@@ -4342,6 +4695,10 @@
       <c r="C89">
         <v>2</v>
       </c>
+      <c r="D89">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
       <c r="E89">
         <v>3329</v>
       </c>
@@ -4362,6 +4719,10 @@
       <c r="C90">
         <v>-1</v>
       </c>
+      <c r="D90">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
       <c r="E90">
         <v>3585</v>
       </c>
@@ -4382,6 +4743,10 @@
       <c r="C91">
         <v>4</v>
       </c>
+      <c r="D91" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92">
@@ -4393,6 +4758,10 @@
       <c r="C92">
         <v>3</v>
       </c>
+      <c r="D92">
+        <f>IF(ISNUMBER(VLOOKUP(A92, $E:$E, 1, FALSE)), 1, "")</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93">
@@ -4404,6 +4773,10 @@
       <c r="C93">
         <v>2</v>
       </c>
+      <c r="D93">
+        <f t="shared" ref="D93:D108" si="2">IF(ISNUMBER(VLOOKUP(A93, $E:$E, 1, FALSE)), 1, "")</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94">
@@ -4415,6 +4788,10 @@
       <c r="C94">
         <v>3</v>
       </c>
+      <c r="D94" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95">
@@ -4426,6 +4803,10 @@
       <c r="C95">
         <v>3</v>
       </c>
+      <c r="D95" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96">
@@ -4437,8 +4818,12 @@
       <c r="C96">
         <v>3</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D96" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>1729</v>
       </c>
@@ -4448,8 +4833,12 @@
       <c r="C97">
         <v>2</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D97">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>1733</v>
       </c>
@@ -4459,8 +4848,12 @@
       <c r="C98">
         <v>3</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D98" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>1737</v>
       </c>
@@ -4470,8 +4863,12 @@
       <c r="C99">
         <v>3</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D99" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>1745</v>
       </c>
@@ -4481,8 +4878,12 @@
       <c r="C100">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D100" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>1761</v>
       </c>
@@ -4492,8 +4893,12 @@
       <c r="C101">
         <v>1</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D101" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>1793</v>
       </c>
@@ -4503,8 +4908,12 @@
       <c r="C102">
         <v>-1</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D102">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>1801</v>
       </c>
@@ -4514,8 +4923,12 @@
       <c r="C103">
         <v>-1</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D103" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>1805</v>
       </c>
@@ -4525,8 +4938,12 @@
       <c r="C104">
         <v>3</v>
       </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D104" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>1809</v>
       </c>
@@ -4536,8 +4953,12 @@
       <c r="C105">
         <v>2</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D105">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>1813</v>
       </c>
@@ -4547,8 +4968,12 @@
       <c r="C106">
         <v>3</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D106" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>1817</v>
       </c>
@@ -4558,8 +4983,12 @@
       <c r="C107">
         <v>3</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D107" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>1825</v>
       </c>
@@ -4569,8 +4998,12 @@
       <c r="C108">
         <v>2</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D108">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>1829</v>
       </c>
@@ -4580,8 +5013,12 @@
       <c r="C109">
         <v>3</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D109" t="str">
+        <f>IF(ISNUMBER(VLOOKUP(A109, $E:$E, 1, FALSE)), 1, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>1833</v>
       </c>
@@ -4591,8 +5028,12 @@
       <c r="C110">
         <v>3</v>
       </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D110" t="str">
+        <f t="shared" ref="D110:D130" si="3">IF(ISNUMBER(VLOOKUP(A110, $E:$E, 1, FALSE)), 1, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>1841</v>
       </c>
@@ -4602,8 +5043,12 @@
       <c r="C111">
         <v>3</v>
       </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D111" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>1857</v>
       </c>
@@ -4613,8 +5058,12 @@
       <c r="C112">
         <v>2</v>
       </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D112">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>1861</v>
       </c>
@@ -4624,8 +5073,12 @@
       <c r="C113">
         <v>3</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D113" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>1865</v>
       </c>
@@ -4635,8 +5088,12 @@
       <c r="C114">
         <v>1</v>
       </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D114" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>1873</v>
       </c>
@@ -4646,8 +5103,12 @@
       <c r="C115">
         <v>1</v>
       </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D115" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>1889</v>
       </c>
@@ -4657,8 +5118,12 @@
       <c r="C116">
         <v>1</v>
       </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D116" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>1921</v>
       </c>
@@ -4668,8 +5133,12 @@
       <c r="C117">
         <v>4</v>
       </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D117">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>1953</v>
       </c>
@@ -4679,8 +5148,12 @@
       <c r="C118">
         <v>1</v>
       </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D118" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>1985</v>
       </c>
@@ -4690,8 +5163,12 @@
       <c r="C119">
         <v>1</v>
       </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D119" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>2049</v>
       </c>
@@ -4701,8 +5178,12 @@
       <c r="C120">
         <v>2</v>
       </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D120">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>2177</v>
       </c>
@@ -4712,8 +5193,12 @@
       <c r="C121">
         <v>-1</v>
       </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D121">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>2209</v>
       </c>
@@ -4723,8 +5208,12 @@
       <c r="C122">
         <v>-1</v>
       </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D122" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>2225</v>
       </c>
@@ -4734,8 +5223,12 @@
       <c r="C123">
         <v>-1</v>
       </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D123" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>2233</v>
       </c>
@@ -4745,8 +5238,12 @@
       <c r="C124">
         <v>-1</v>
       </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D124" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>2237</v>
       </c>
@@ -4756,8 +5253,12 @@
       <c r="C125">
         <v>3</v>
       </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D125" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>2241</v>
       </c>
@@ -4767,8 +5268,12 @@
       <c r="C126">
         <v>-1</v>
       </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D126">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>2257</v>
       </c>
@@ -4778,8 +5283,12 @@
       <c r="C127">
         <v>2</v>
       </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D127" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>2265</v>
       </c>
@@ -4789,8 +5298,12 @@
       <c r="C128">
         <v>2</v>
       </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D128" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>2269</v>
       </c>
@@ -4800,8 +5313,12 @@
       <c r="C129">
         <v>3</v>
       </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D129" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>2273</v>
       </c>
@@ -4811,8 +5328,12 @@
       <c r="C130">
         <v>2</v>
       </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D130">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>2281</v>
       </c>
@@ -4822,8 +5343,12 @@
       <c r="C131">
         <v>2</v>
       </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D131" t="str">
+        <f>IF(ISNUMBER(VLOOKUP(A131, $E:$E, 1, FALSE)), 1, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>2285</v>
       </c>
@@ -4833,8 +5358,12 @@
       <c r="C132">
         <v>3</v>
       </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D132" t="str">
+        <f t="shared" ref="D132:D151" si="4">IF(ISNUMBER(VLOOKUP(A132, $E:$E, 1, FALSE)), 1, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>2289</v>
       </c>
@@ -4844,8 +5373,12 @@
       <c r="C133">
         <v>2</v>
       </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D133">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>2293</v>
       </c>
@@ -4855,8 +5388,12 @@
       <c r="C134">
         <v>1</v>
       </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D134" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>2297</v>
       </c>
@@ -4866,8 +5403,12 @@
       <c r="C135">
         <v>1</v>
       </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D135" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>2305</v>
       </c>
@@ -4877,8 +5418,12 @@
       <c r="C136">
         <v>-1</v>
       </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D136">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>2337</v>
       </c>
@@ -4888,8 +5433,12 @@
       <c r="C137">
         <v>2</v>
       </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D137" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>2353</v>
       </c>
@@ -4899,8 +5448,12 @@
       <c r="C138">
         <v>2</v>
       </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D138" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>2361</v>
       </c>
@@ -4910,8 +5463,12 @@
       <c r="C139">
         <v>2</v>
       </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D139" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>2365</v>
       </c>
@@ -4921,8 +5478,12 @@
       <c r="C140">
         <v>3</v>
       </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D140" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>2369</v>
       </c>
@@ -4932,8 +5493,12 @@
       <c r="C141">
         <v>2</v>
       </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D141">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>2385</v>
       </c>
@@ -4943,8 +5508,12 @@
       <c r="C142">
         <v>2</v>
       </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D142">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>2393</v>
       </c>
@@ -4954,8 +5523,12 @@
       <c r="C143">
         <v>4</v>
       </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D143">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>2401</v>
       </c>
@@ -4965,8 +5538,12 @@
       <c r="C144">
         <v>-1</v>
       </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D144">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>2405</v>
       </c>
@@ -4976,8 +5553,12 @@
       <c r="C145">
         <v>4</v>
       </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D145" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>2409</v>
       </c>
@@ -4987,8 +5568,12 @@
       <c r="C146">
         <v>3</v>
       </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D146">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>2417</v>
       </c>
@@ -4998,8 +5583,12 @@
       <c r="C147">
         <v>3</v>
       </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D147">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>2433</v>
       </c>
@@ -5009,8 +5598,12 @@
       <c r="C148">
         <v>2</v>
       </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D148">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>2449</v>
       </c>
@@ -5020,8 +5613,12 @@
       <c r="C149">
         <v>-1</v>
       </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D149">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>2453</v>
       </c>
@@ -5031,8 +5628,12 @@
       <c r="C150">
         <v>3</v>
       </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D150" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>2457</v>
       </c>
@@ -5042,8 +5643,12 @@
       <c r="C151">
         <v>3</v>
       </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D151" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>2465</v>
       </c>
@@ -5053,8 +5658,12 @@
       <c r="C152">
         <v>2</v>
       </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D152">
+        <f>IF(ISNUMBER(VLOOKUP(A152, $E:$E, 1, FALSE)), 1, "")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>2469</v>
       </c>
@@ -5064,8 +5673,12 @@
       <c r="C153">
         <v>3</v>
       </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D153" t="str">
+        <f t="shared" ref="D153:D167" si="5">IF(ISNUMBER(VLOOKUP(A153, $E:$E, 1, FALSE)), 1, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>2473</v>
       </c>
@@ -5075,8 +5688,12 @@
       <c r="C154">
         <v>3</v>
       </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D154" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>2481</v>
       </c>
@@ -5086,8 +5703,12 @@
       <c r="C155">
         <v>3</v>
       </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D155" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>2497</v>
       </c>
@@ -5097,8 +5718,12 @@
       <c r="C156">
         <v>2</v>
       </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D156">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>2501</v>
       </c>
@@ -5108,8 +5733,12 @@
       <c r="C157">
         <v>3</v>
       </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D157" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>2505</v>
       </c>
@@ -5119,8 +5748,12 @@
       <c r="C158">
         <v>1</v>
       </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D158" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>2513</v>
       </c>
@@ -5130,8 +5763,12 @@
       <c r="C159">
         <v>1</v>
       </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D159" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>2529</v>
       </c>
@@ -5141,8 +5778,12 @@
       <c r="C160">
         <v>1</v>
       </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D160" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>2561</v>
       </c>
@@ -5152,8 +5793,12 @@
       <c r="C161">
         <v>2</v>
       </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D161">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>2593</v>
       </c>
@@ -5163,8 +5808,12 @@
       <c r="C162">
         <v>2</v>
       </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D162">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>2609</v>
       </c>
@@ -5174,8 +5823,12 @@
       <c r="C163">
         <v>-1</v>
       </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D163">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>2613</v>
       </c>
@@ -5185,8 +5838,12 @@
       <c r="C164">
         <v>4</v>
       </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D164" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>2617</v>
       </c>
@@ -5196,8 +5853,12 @@
       <c r="C165">
         <v>3</v>
       </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D165">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>2625</v>
       </c>
@@ -5207,8 +5868,12 @@
       <c r="C166">
         <v>-1</v>
       </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D166">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>2633</v>
       </c>
@@ -5218,8 +5883,12 @@
       <c r="C167">
         <v>-1</v>
       </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D167" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>2637</v>
       </c>
@@ -5229,8 +5898,12 @@
       <c r="C168">
         <v>3</v>
       </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D168" t="str">
+        <f>IF(ISNUMBER(VLOOKUP(A168, $E:$E, 1, FALSE)), 1, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>2641</v>
       </c>
@@ -5240,8 +5913,12 @@
       <c r="C169">
         <v>2</v>
       </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D169">
+        <f t="shared" ref="D169:D190" si="6">IF(ISNUMBER(VLOOKUP(A169, $E:$E, 1, FALSE)), 1, "")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>2645</v>
       </c>
@@ -5251,8 +5928,12 @@
       <c r="C170">
         <v>3</v>
       </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D170" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>2649</v>
       </c>
@@ -5262,8 +5943,12 @@
       <c r="C171">
         <v>3</v>
       </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D171" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>2657</v>
       </c>
@@ -5273,8 +5958,12 @@
       <c r="C172">
         <v>2</v>
       </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D172">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>2661</v>
       </c>
@@ -5284,8 +5973,12 @@
       <c r="C173">
         <v>3</v>
       </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D173" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>2665</v>
       </c>
@@ -5295,8 +5988,12 @@
       <c r="C174">
         <v>3</v>
       </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D174" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>2673</v>
       </c>
@@ -5306,8 +6003,12 @@
       <c r="C175">
         <v>3</v>
       </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D175" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>2689</v>
       </c>
@@ -5317,8 +6018,12 @@
       <c r="C176">
         <v>2</v>
       </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D176">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>2697</v>
       </c>
@@ -5328,8 +6033,12 @@
       <c r="C177">
         <v>2</v>
       </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D177" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>2701</v>
       </c>
@@ -5339,8 +6048,12 @@
       <c r="C178">
         <v>3</v>
       </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D178" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>2705</v>
       </c>
@@ -5350,8 +6063,12 @@
       <c r="C179">
         <v>2</v>
       </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D179">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>2709</v>
       </c>
@@ -5361,8 +6078,12 @@
       <c r="C180">
         <v>3</v>
       </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D180" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>2713</v>
       </c>
@@ -5372,8 +6093,12 @@
       <c r="C181">
         <v>3</v>
       </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D181" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>2721</v>
       </c>
@@ -5383,8 +6108,12 @@
       <c r="C182">
         <v>2</v>
       </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D182">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>2725</v>
       </c>
@@ -5394,8 +6123,12 @@
       <c r="C183">
         <v>1</v>
       </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D183" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>2729</v>
       </c>
@@ -5405,8 +6138,12 @@
       <c r="C184">
         <v>1</v>
       </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D184" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>2737</v>
       </c>
@@ -5416,8 +6153,12 @@
       <c r="C185">
         <v>1</v>
       </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D185" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>2753</v>
       </c>
@@ -5427,8 +6168,12 @@
       <c r="C186">
         <v>4</v>
       </c>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D186">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>2785</v>
       </c>
@@ -5438,8 +6183,12 @@
       <c r="C187">
         <v>1</v>
       </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D187" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>2817</v>
       </c>
@@ -5449,8 +6198,12 @@
       <c r="C188">
         <v>2</v>
       </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D188">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>2825</v>
       </c>
@@ -5460,8 +6213,12 @@
       <c r="C189">
         <v>2</v>
       </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D189" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>2829</v>
       </c>
@@ -5471,8 +6228,12 @@
       <c r="C190">
         <v>3</v>
       </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D190" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>2833</v>
       </c>
@@ -5482,8 +6243,12 @@
       <c r="C191">
         <v>4</v>
       </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D191">
+        <f>IF(ISNUMBER(VLOOKUP(A191, $E:$E, 1, FALSE)), 1, "")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>2849</v>
       </c>
@@ -5493,8 +6258,12 @@
       <c r="C192">
         <v>3</v>
       </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D192">
+        <f t="shared" ref="D192:D214" si="7">IF(ISNUMBER(VLOOKUP(A192, $E:$E, 1, FALSE)), 1, "")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>2881</v>
       </c>
@@ -5504,8 +6273,12 @@
       <c r="C193">
         <v>3</v>
       </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D193">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>2945</v>
       </c>
@@ -5515,8 +6288,12 @@
       <c r="C194">
         <v>3</v>
       </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D194">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>3073</v>
       </c>
@@ -5526,8 +6303,12 @@
       <c r="C195">
         <v>-1</v>
       </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D195">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>3089</v>
       </c>
@@ -5537,8 +6318,12 @@
       <c r="C196">
         <v>-1</v>
       </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D196" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>3097</v>
       </c>
@@ -5548,8 +6333,12 @@
       <c r="C197">
         <v>-1</v>
       </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D197" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>3101</v>
       </c>
@@ -5559,8 +6348,12 @@
       <c r="C198">
         <v>3</v>
       </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D198" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>3105</v>
       </c>
@@ -5570,8 +6363,12 @@
       <c r="C199">
         <v>-1</v>
       </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D199">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>3113</v>
       </c>
@@ -5581,8 +6378,12 @@
       <c r="C200">
         <v>2</v>
       </c>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D200" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>3117</v>
       </c>
@@ -5592,8 +6393,12 @@
       <c r="C201">
         <v>3</v>
       </c>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D201" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>3121</v>
       </c>
@@ -5603,8 +6408,12 @@
       <c r="C202">
         <v>2</v>
       </c>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D202">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>3125</v>
       </c>
@@ -5614,8 +6423,12 @@
       <c r="C203">
         <v>3</v>
       </c>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D203" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>3129</v>
       </c>
@@ -5625,8 +6438,12 @@
       <c r="C204">
         <v>3</v>
       </c>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D204" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>3137</v>
       </c>
@@ -5636,8 +6453,12 @@
       <c r="C205">
         <v>2</v>
       </c>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D205">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>3145</v>
       </c>
@@ -5647,8 +6468,12 @@
       <c r="C206">
         <v>2</v>
       </c>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D206" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>3149</v>
       </c>
@@ -5658,8 +6483,12 @@
       <c r="C207">
         <v>3</v>
       </c>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D207" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>3153</v>
       </c>
@@ -5669,8 +6498,12 @@
       <c r="C208">
         <v>2</v>
       </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D208">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>3157</v>
       </c>
@@ -5680,8 +6513,12 @@
       <c r="C209">
         <v>3</v>
       </c>
-    </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D209" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>3161</v>
       </c>
@@ -5691,8 +6528,12 @@
       <c r="C210">
         <v>1</v>
       </c>
-    </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D210" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>3169</v>
       </c>
@@ -5702,8 +6543,12 @@
       <c r="C211">
         <v>4</v>
       </c>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D211">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>3201</v>
       </c>
@@ -5713,8 +6558,12 @@
       <c r="C212">
         <v>2</v>
       </c>
-    </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D212">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>3209</v>
       </c>
@@ -5724,8 +6573,12 @@
       <c r="C213">
         <v>4</v>
       </c>
-    </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D213">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>3217</v>
       </c>
@@ -5735,8 +6588,12 @@
       <c r="C214">
         <v>3</v>
       </c>
-    </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D214">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>3233</v>
       </c>
@@ -5746,8 +6603,12 @@
       <c r="C215">
         <v>3</v>
       </c>
-    </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D215">
+        <f>IF(ISNUMBER(VLOOKUP(A215, $E:$E, 1, FALSE)), 1, "")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>3265</v>
       </c>
@@ -5757,8 +6618,12 @@
       <c r="C216">
         <v>3</v>
       </c>
-    </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D216">
+        <f t="shared" ref="D216:D233" si="8">IF(ISNUMBER(VLOOKUP(A216, $E:$E, 1, FALSE)), 1, "")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>3329</v>
       </c>
@@ -5768,8 +6633,12 @@
       <c r="C217">
         <v>-1</v>
       </c>
-    </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D217">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>3333</v>
       </c>
@@ -5779,8 +6648,12 @@
       <c r="C218">
         <v>3</v>
       </c>
-    </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D218" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>3337</v>
       </c>
@@ -5790,8 +6663,12 @@
       <c r="C219">
         <v>3</v>
       </c>
-    </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D219" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>3345</v>
       </c>
@@ -5801,8 +6678,12 @@
       <c r="C220">
         <v>3</v>
       </c>
-    </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D220" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>3361</v>
       </c>
@@ -5812,8 +6693,12 @@
       <c r="C221">
         <v>3</v>
       </c>
-    </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D221" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>3393</v>
       </c>
@@ -5823,8 +6708,12 @@
       <c r="C222">
         <v>3</v>
       </c>
-    </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D222" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>3457</v>
       </c>
@@ -5834,8 +6723,12 @@
       <c r="C223">
         <v>3</v>
       </c>
-    </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D223" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>3585</v>
       </c>
@@ -5845,8 +6738,12 @@
       <c r="C224">
         <v>2</v>
       </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D224">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>3589</v>
       </c>
@@ -5856,8 +6753,12 @@
       <c r="C225">
         <v>3</v>
       </c>
-    </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D225" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>3593</v>
       </c>
@@ -5867,8 +6768,12 @@
       <c r="C226">
         <v>3</v>
       </c>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D226" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>3601</v>
       </c>
@@ -5878,8 +6783,12 @@
       <c r="C227">
         <v>3</v>
       </c>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D227" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>3617</v>
       </c>
@@ -5889,8 +6798,12 @@
       <c r="C228">
         <v>3</v>
       </c>
-    </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D228" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>3649</v>
       </c>
@@ -5900,8 +6813,12 @@
       <c r="C229">
         <v>1</v>
       </c>
-    </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D229" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>3713</v>
       </c>
@@ -5911,8 +6828,12 @@
       <c r="C230">
         <v>1</v>
       </c>
-    </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D230" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>3841</v>
       </c>
@@ -5921,6 +6842,22 @@
       </c>
       <c r="C231">
         <v>1</v>
+      </c>
+      <c r="D231" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D232" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D233" t="str">
+        <f t="shared" si="8"/>
+        <v/>
       </c>
     </row>
     <row r="1048576" spans="8:8" x14ac:dyDescent="0.25">
@@ -6352,27 +7289,27 @@
         <v>12</v>
       </c>
       <c r="K10">
-        <f>K5/C5</f>
+        <f t="shared" ref="K10:P10" si="7">K5/C5</f>
         <v>0</v>
       </c>
       <c r="L10">
-        <f>L5/D5</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M10">
-        <f>M5/E5</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="N10">
-        <f>N5/F5</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="O10">
-        <f>O5/G5</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="P10">
-        <f>P5/H5</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -6388,23 +7325,23 @@
         <v>18</v>
       </c>
       <c r="D12">
-        <f t="shared" ref="D12:H12" si="7">D7-L2</f>
+        <f t="shared" ref="D12:H12" si="8">D7-L2</f>
         <v>20</v>
       </c>
       <c r="E12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>17</v>
       </c>
       <c r="F12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>54</v>
       </c>
       <c r="G12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>68</v>
       </c>
       <c r="H12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>60</v>
       </c>
     </row>
@@ -6413,27 +7350,27 @@
         <v>10</v>
       </c>
       <c r="C13">
-        <f t="shared" ref="C13:C15" si="8">C8-K3</f>
+        <f t="shared" ref="C13:C15" si="9">C8-K3</f>
         <v>16</v>
       </c>
       <c r="D13">
-        <f t="shared" ref="D13:D15" si="9">D8-L3</f>
+        <f t="shared" ref="D13:D15" si="10">D8-L3</f>
         <v>18</v>
       </c>
       <c r="E13">
-        <f t="shared" ref="E13:E15" si="10">E8-M3</f>
+        <f t="shared" ref="E13:E15" si="11">E8-M3</f>
         <v>16</v>
       </c>
       <c r="F13">
-        <f t="shared" ref="F13:F15" si="11">F8-N3</f>
+        <f t="shared" ref="F13:F15" si="12">F8-N3</f>
         <v>43</v>
       </c>
       <c r="G13">
-        <f t="shared" ref="G13:G15" si="12">G8-O3</f>
+        <f t="shared" ref="G13:G15" si="13">G8-O3</f>
         <v>58</v>
       </c>
       <c r="H13">
-        <f t="shared" ref="H13:H15" si="13">H8-P3</f>
+        <f t="shared" ref="H13:H15" si="14">H8-P3</f>
         <v>51</v>
       </c>
     </row>
@@ -6442,27 +7379,27 @@
         <v>11</v>
       </c>
       <c r="C14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>17</v>
       </c>
       <c r="D14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>22</v>
       </c>
       <c r="E14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>17</v>
       </c>
       <c r="F14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>49</v>
       </c>
       <c r="G14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>62</v>
       </c>
       <c r="H14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>57</v>
       </c>
     </row>
@@ -6471,27 +7408,27 @@
         <v>12</v>
       </c>
       <c r="C15">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>13</v>
       </c>
       <c r="D15">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="E15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>15</v>
       </c>
       <c r="F15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>40</v>
       </c>
       <c r="G15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>47</v>
       </c>
       <c r="H15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>40</v>
       </c>
     </row>
@@ -6609,4 +7546,3618 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33F8C8D1-2097-4368-9F61-CF173B408D0C}">
+  <dimension ref="A2:H186"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>512</v>
+      </c>
+      <c r="C2">
+        <v>-1</v>
+      </c>
+      <c r="D2">
+        <f>IF(ISNUMBER(VLOOKUP(A2, $E:$E, 1, FALSE)), 1, "")</f>
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1024</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>513</v>
+      </c>
+      <c r="B3">
+        <v>256</v>
+      </c>
+      <c r="C3">
+        <v>-1</v>
+      </c>
+      <c r="D3" t="str">
+        <f t="shared" ref="D3:D66" si="0">IF(ISNUMBER(VLOOKUP(A3, $E:$E, 1, FALSE)), 1, "")</f>
+        <v/>
+      </c>
+      <c r="E3">
+        <v>1025</v>
+      </c>
+      <c r="F3">
+        <v>256</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>769</v>
+      </c>
+      <c r="B4">
+        <v>128</v>
+      </c>
+      <c r="C4">
+        <v>-1</v>
+      </c>
+      <c r="D4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E4">
+        <v>1281</v>
+      </c>
+      <c r="F4">
+        <v>128</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>897</v>
+      </c>
+      <c r="B5">
+        <v>64</v>
+      </c>
+      <c r="C5">
+        <v>-1</v>
+      </c>
+      <c r="D5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E5">
+        <v>1409</v>
+      </c>
+      <c r="F5">
+        <v>64</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>961</v>
+      </c>
+      <c r="B6">
+        <v>32</v>
+      </c>
+      <c r="C6">
+        <v>-1</v>
+      </c>
+      <c r="D6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E6">
+        <v>1473</v>
+      </c>
+      <c r="F6">
+        <v>32</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>993</v>
+      </c>
+      <c r="B7">
+        <v>16</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E7">
+        <v>1505</v>
+      </c>
+      <c r="F7">
+        <v>16</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>1009</v>
+      </c>
+      <c r="B8">
+        <v>8</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E8">
+        <v>1521</v>
+      </c>
+      <c r="F8">
+        <v>8</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>1017</v>
+      </c>
+      <c r="B9">
+        <v>4</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E9">
+        <v>1529</v>
+      </c>
+      <c r="F9">
+        <v>8</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+      <c r="H9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>1021</v>
+      </c>
+      <c r="B10">
+        <v>4</v>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+      <c r="D10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E10">
+        <v>1537</v>
+      </c>
+      <c r="F10">
+        <v>128</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>1025</v>
+      </c>
+      <c r="B11">
+        <v>256</v>
+      </c>
+      <c r="C11">
+        <v>-1</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>1665</v>
+      </c>
+      <c r="F11">
+        <v>64</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>1281</v>
+      </c>
+      <c r="B12">
+        <v>128</v>
+      </c>
+      <c r="C12">
+        <v>-1</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>1729</v>
+      </c>
+      <c r="F12">
+        <v>32</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>1409</v>
+      </c>
+      <c r="B13">
+        <v>64</v>
+      </c>
+      <c r="C13">
+        <v>-1</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1761</v>
+      </c>
+      <c r="F13">
+        <v>16</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>1473</v>
+      </c>
+      <c r="B14">
+        <v>32</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>1777</v>
+      </c>
+      <c r="F14">
+        <v>16</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+      <c r="H14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>1505</v>
+      </c>
+      <c r="B15">
+        <v>16</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>1793</v>
+      </c>
+      <c r="F15">
+        <v>64</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>1521</v>
+      </c>
+      <c r="B16">
+        <v>8</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>1857</v>
+      </c>
+      <c r="F16">
+        <v>32</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>1529</v>
+      </c>
+      <c r="B17">
+        <v>8</v>
+      </c>
+      <c r="C17">
+        <v>3</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>1889</v>
+      </c>
+      <c r="F17">
+        <v>16</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>1537</v>
+      </c>
+      <c r="B18">
+        <v>128</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>1905</v>
+      </c>
+      <c r="F18">
+        <v>16</v>
+      </c>
+      <c r="G18">
+        <v>2</v>
+      </c>
+      <c r="H18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>1665</v>
+      </c>
+      <c r="B19">
+        <v>64</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>1921</v>
+      </c>
+      <c r="F19">
+        <v>32</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>1729</v>
+      </c>
+      <c r="B20">
+        <v>16</v>
+      </c>
+      <c r="C20">
+        <v>-1</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>1953</v>
+      </c>
+      <c r="F20">
+        <v>8</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>1745</v>
+      </c>
+      <c r="B21">
+        <v>8</v>
+      </c>
+      <c r="C21">
+        <v>-1</v>
+      </c>
+      <c r="D21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E21">
+        <v>1961</v>
+      </c>
+      <c r="F21">
+        <v>8</v>
+      </c>
+      <c r="G21">
+        <v>2</v>
+      </c>
+      <c r="H21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>1753</v>
+      </c>
+      <c r="B22">
+        <v>4</v>
+      </c>
+      <c r="C22">
+        <v>-1</v>
+      </c>
+      <c r="D22" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E22">
+        <v>1969</v>
+      </c>
+      <c r="F22">
+        <v>16</v>
+      </c>
+      <c r="G22">
+        <v>2</v>
+      </c>
+      <c r="H22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>1757</v>
+      </c>
+      <c r="B23">
+        <v>4</v>
+      </c>
+      <c r="C23">
+        <v>4</v>
+      </c>
+      <c r="D23" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E23">
+        <v>1985</v>
+      </c>
+      <c r="F23">
+        <v>64</v>
+      </c>
+      <c r="G23">
+        <v>2</v>
+      </c>
+      <c r="H23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>1761</v>
+      </c>
+      <c r="B24">
+        <v>8</v>
+      </c>
+      <c r="C24">
+        <v>-1</v>
+      </c>
+      <c r="D24">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <v>2049</v>
+      </c>
+      <c r="F24">
+        <v>256</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>1769</v>
+      </c>
+      <c r="B25">
+        <v>4</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+      <c r="D25" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E25">
+        <v>2305</v>
+      </c>
+      <c r="F25">
+        <v>128</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>1773</v>
+      </c>
+      <c r="B26">
+        <v>4</v>
+      </c>
+      <c r="C26">
+        <v>3</v>
+      </c>
+      <c r="D26" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E26">
+        <v>2433</v>
+      </c>
+      <c r="F26">
+        <v>64</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>1777</v>
+      </c>
+      <c r="B27">
+        <v>4</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+      <c r="D27">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <v>2497</v>
+      </c>
+      <c r="F27">
+        <v>32</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>1781</v>
+      </c>
+      <c r="B28">
+        <v>4</v>
+      </c>
+      <c r="C28">
+        <v>3</v>
+      </c>
+      <c r="D28" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E28">
+        <v>2529</v>
+      </c>
+      <c r="F28">
+        <v>16</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>1785</v>
+      </c>
+      <c r="B29">
+        <v>8</v>
+      </c>
+      <c r="C29">
+        <v>3</v>
+      </c>
+      <c r="D29" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E29">
+        <v>2545</v>
+      </c>
+      <c r="F29">
+        <v>16</v>
+      </c>
+      <c r="G29">
+        <v>2</v>
+      </c>
+      <c r="H29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>1793</v>
+      </c>
+      <c r="B30">
+        <v>32</v>
+      </c>
+      <c r="C30">
+        <v>-1</v>
+      </c>
+      <c r="D30">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E30">
+        <v>2561</v>
+      </c>
+      <c r="F30">
+        <v>128</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>1825</v>
+      </c>
+      <c r="B31">
+        <v>16</v>
+      </c>
+      <c r="C31">
+        <v>-1</v>
+      </c>
+      <c r="D31" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E31">
+        <v>2689</v>
+      </c>
+      <c r="F31">
+        <v>64</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+      <c r="H31">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>1841</v>
+      </c>
+      <c r="B32">
+        <v>8</v>
+      </c>
+      <c r="C32">
+        <v>-1</v>
+      </c>
+      <c r="D32" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E32">
+        <v>2753</v>
+      </c>
+      <c r="F32">
+        <v>32</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="H32">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>1849</v>
+      </c>
+      <c r="B33">
+        <v>4</v>
+      </c>
+      <c r="C33">
+        <v>-1</v>
+      </c>
+      <c r="D33" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E33">
+        <v>2785</v>
+      </c>
+      <c r="F33">
+        <v>8</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+      <c r="H33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>1853</v>
+      </c>
+      <c r="B34">
+        <v>4</v>
+      </c>
+      <c r="C34">
+        <v>3</v>
+      </c>
+      <c r="D34" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E34">
+        <v>2793</v>
+      </c>
+      <c r="F34">
+        <v>8</v>
+      </c>
+      <c r="G34">
+        <v>2</v>
+      </c>
+      <c r="H34">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>1857</v>
+      </c>
+      <c r="B35">
+        <v>16</v>
+      </c>
+      <c r="C35">
+        <v>-1</v>
+      </c>
+      <c r="D35">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E35">
+        <v>2801</v>
+      </c>
+      <c r="F35">
+        <v>16</v>
+      </c>
+      <c r="G35">
+        <v>2</v>
+      </c>
+      <c r="H35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>1873</v>
+      </c>
+      <c r="B36">
+        <v>8</v>
+      </c>
+      <c r="C36">
+        <v>2</v>
+      </c>
+      <c r="D36" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E36">
+        <v>2817</v>
+      </c>
+      <c r="F36">
+        <v>64</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+      <c r="H36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>1881</v>
+      </c>
+      <c r="B37">
+        <v>4</v>
+      </c>
+      <c r="C37">
+        <v>2</v>
+      </c>
+      <c r="D37" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E37">
+        <v>2881</v>
+      </c>
+      <c r="F37">
+        <v>16</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+      <c r="H37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>1885</v>
+      </c>
+      <c r="B38">
+        <v>4</v>
+      </c>
+      <c r="C38">
+        <v>3</v>
+      </c>
+      <c r="D38" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E38">
+        <v>2897</v>
+      </c>
+      <c r="F38">
+        <v>8</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+      <c r="H38">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>1889</v>
+      </c>
+      <c r="B39">
+        <v>8</v>
+      </c>
+      <c r="C39">
+        <v>2</v>
+      </c>
+      <c r="D39">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E39">
+        <v>2905</v>
+      </c>
+      <c r="F39">
+        <v>8</v>
+      </c>
+      <c r="G39">
+        <v>2</v>
+      </c>
+      <c r="H39">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>1897</v>
+      </c>
+      <c r="B40">
+        <v>4</v>
+      </c>
+      <c r="C40">
+        <v>2</v>
+      </c>
+      <c r="D40" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E40">
+        <v>2913</v>
+      </c>
+      <c r="F40">
+        <v>32</v>
+      </c>
+      <c r="G40">
+        <v>2</v>
+      </c>
+      <c r="H40">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>1901</v>
+      </c>
+      <c r="B41">
+        <v>4</v>
+      </c>
+      <c r="C41">
+        <v>3</v>
+      </c>
+      <c r="D41" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E41">
+        <v>2945</v>
+      </c>
+      <c r="F41">
+        <v>16</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+      <c r="H41">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>1905</v>
+      </c>
+      <c r="B42">
+        <v>4</v>
+      </c>
+      <c r="C42">
+        <v>2</v>
+      </c>
+      <c r="D42">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E42">
+        <v>2961</v>
+      </c>
+      <c r="F42">
+        <v>16</v>
+      </c>
+      <c r="G42">
+        <v>2</v>
+      </c>
+      <c r="H42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>1909</v>
+      </c>
+      <c r="B43">
+        <v>4</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+      <c r="D43" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E43">
+        <v>2977</v>
+      </c>
+      <c r="F43">
+        <v>32</v>
+      </c>
+      <c r="G43">
+        <v>2</v>
+      </c>
+      <c r="H43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>1913</v>
+      </c>
+      <c r="B44">
+        <v>8</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+      <c r="D44" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E44">
+        <v>3009</v>
+      </c>
+      <c r="F44">
+        <v>64</v>
+      </c>
+      <c r="G44">
+        <v>2</v>
+      </c>
+      <c r="H44">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>1921</v>
+      </c>
+      <c r="B45">
+        <v>16</v>
+      </c>
+      <c r="C45">
+        <v>2</v>
+      </c>
+      <c r="D45">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E45">
+        <v>3073</v>
+      </c>
+      <c r="F45">
+        <v>128</v>
+      </c>
+      <c r="G45">
+        <v>1</v>
+      </c>
+      <c r="H45">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>1937</v>
+      </c>
+      <c r="B46">
+        <v>8</v>
+      </c>
+      <c r="C46">
+        <v>2</v>
+      </c>
+      <c r="D46" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E46">
+        <v>3201</v>
+      </c>
+      <c r="F46">
+        <v>32</v>
+      </c>
+      <c r="G46">
+        <v>1</v>
+      </c>
+      <c r="H46">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>1945</v>
+      </c>
+      <c r="B47">
+        <v>4</v>
+      </c>
+      <c r="C47">
+        <v>2</v>
+      </c>
+      <c r="D47" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E47">
+        <v>3233</v>
+      </c>
+      <c r="F47">
+        <v>16</v>
+      </c>
+      <c r="G47">
+        <v>1</v>
+      </c>
+      <c r="H47">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>1949</v>
+      </c>
+      <c r="B48">
+        <v>4</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+      <c r="D48" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E48">
+        <v>3249</v>
+      </c>
+      <c r="F48">
+        <v>8</v>
+      </c>
+      <c r="G48">
+        <v>1</v>
+      </c>
+      <c r="H48">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>1953</v>
+      </c>
+      <c r="B49">
+        <v>8</v>
+      </c>
+      <c r="C49">
+        <v>2</v>
+      </c>
+      <c r="D49">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E49">
+        <v>3257</v>
+      </c>
+      <c r="F49">
+        <v>8</v>
+      </c>
+      <c r="G49">
+        <v>2</v>
+      </c>
+      <c r="H49">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>1961</v>
+      </c>
+      <c r="B50">
+        <v>8</v>
+      </c>
+      <c r="C50">
+        <v>3</v>
+      </c>
+      <c r="D50">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E50">
+        <v>3265</v>
+      </c>
+      <c r="F50">
+        <v>16</v>
+      </c>
+      <c r="G50">
+        <v>1</v>
+      </c>
+      <c r="H50">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>1969</v>
+      </c>
+      <c r="B51">
+        <v>16</v>
+      </c>
+      <c r="C51">
+        <v>3</v>
+      </c>
+      <c r="D51">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E51">
+        <v>3281</v>
+      </c>
+      <c r="F51">
+        <v>16</v>
+      </c>
+      <c r="G51">
+        <v>2</v>
+      </c>
+      <c r="H51">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>1985</v>
+      </c>
+      <c r="B52">
+        <v>4</v>
+      </c>
+      <c r="C52">
+        <v>2</v>
+      </c>
+      <c r="D52">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E52">
+        <v>3297</v>
+      </c>
+      <c r="F52">
+        <v>32</v>
+      </c>
+      <c r="G52">
+        <v>2</v>
+      </c>
+      <c r="H52">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>1989</v>
+      </c>
+      <c r="B53">
+        <v>4</v>
+      </c>
+      <c r="C53">
+        <v>3</v>
+      </c>
+      <c r="D53" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E53">
+        <v>3329</v>
+      </c>
+      <c r="F53">
+        <v>32</v>
+      </c>
+      <c r="G53">
+        <v>1</v>
+      </c>
+      <c r="H53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>1993</v>
+      </c>
+      <c r="B54">
+        <v>8</v>
+      </c>
+      <c r="C54">
+        <v>3</v>
+      </c>
+      <c r="D54" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E54">
+        <v>3361</v>
+      </c>
+      <c r="F54">
+        <v>16</v>
+      </c>
+      <c r="G54">
+        <v>1</v>
+      </c>
+      <c r="H54">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>2001</v>
+      </c>
+      <c r="B55">
+        <v>16</v>
+      </c>
+      <c r="C55">
+        <v>3</v>
+      </c>
+      <c r="D55" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E55">
+        <v>3377</v>
+      </c>
+      <c r="F55">
+        <v>16</v>
+      </c>
+      <c r="G55">
+        <v>2</v>
+      </c>
+      <c r="H55">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>2017</v>
+      </c>
+      <c r="B56">
+        <v>32</v>
+      </c>
+      <c r="C56">
+        <v>3</v>
+      </c>
+      <c r="D56" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E56">
+        <v>3393</v>
+      </c>
+      <c r="F56">
+        <v>16</v>
+      </c>
+      <c r="G56">
+        <v>1</v>
+      </c>
+      <c r="H56">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>2049</v>
+      </c>
+      <c r="B57">
+        <v>256</v>
+      </c>
+      <c r="C57">
+        <v>2</v>
+      </c>
+      <c r="D57">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E57">
+        <v>3409</v>
+      </c>
+      <c r="F57">
+        <v>16</v>
+      </c>
+      <c r="G57">
+        <v>2</v>
+      </c>
+      <c r="H57">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>2305</v>
+      </c>
+      <c r="B58">
+        <v>128</v>
+      </c>
+      <c r="C58">
+        <v>2</v>
+      </c>
+      <c r="D58">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E58">
+        <v>3425</v>
+      </c>
+      <c r="F58">
+        <v>32</v>
+      </c>
+      <c r="G58">
+        <v>2</v>
+      </c>
+      <c r="H58">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>2433</v>
+      </c>
+      <c r="B59">
+        <v>64</v>
+      </c>
+      <c r="C59">
+        <v>2</v>
+      </c>
+      <c r="D59">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E59">
+        <v>3457</v>
+      </c>
+      <c r="F59">
+        <v>16</v>
+      </c>
+      <c r="G59">
+        <v>1</v>
+      </c>
+      <c r="H59">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>2497</v>
+      </c>
+      <c r="B60">
+        <v>16</v>
+      </c>
+      <c r="C60">
+        <v>-1</v>
+      </c>
+      <c r="D60">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E60">
+        <v>3473</v>
+      </c>
+      <c r="F60">
+        <v>16</v>
+      </c>
+      <c r="G60">
+        <v>2</v>
+      </c>
+      <c r="H60">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>2513</v>
+      </c>
+      <c r="B61">
+        <v>8</v>
+      </c>
+      <c r="C61">
+        <v>-1</v>
+      </c>
+      <c r="D61" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E61">
+        <v>3489</v>
+      </c>
+      <c r="F61">
+        <v>32</v>
+      </c>
+      <c r="G61">
+        <v>2</v>
+      </c>
+      <c r="H61">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>2521</v>
+      </c>
+      <c r="B62">
+        <v>4</v>
+      </c>
+      <c r="C62">
+        <v>-1</v>
+      </c>
+      <c r="D62" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E62">
+        <v>3521</v>
+      </c>
+      <c r="F62">
+        <v>64</v>
+      </c>
+      <c r="G62">
+        <v>2</v>
+      </c>
+      <c r="H62">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>2525</v>
+      </c>
+      <c r="B63">
+        <v>4</v>
+      </c>
+      <c r="C63">
+        <v>3</v>
+      </c>
+      <c r="D63" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E63">
+        <v>3585</v>
+      </c>
+      <c r="F63">
+        <v>32</v>
+      </c>
+      <c r="G63">
+        <v>1</v>
+      </c>
+      <c r="H63">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>2529</v>
+      </c>
+      <c r="B64">
+        <v>8</v>
+      </c>
+      <c r="C64">
+        <v>2</v>
+      </c>
+      <c r="D64">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E64">
+        <v>3617</v>
+      </c>
+      <c r="F64">
+        <v>16</v>
+      </c>
+      <c r="G64">
+        <v>1</v>
+      </c>
+      <c r="H64">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>2537</v>
+      </c>
+      <c r="B65">
+        <v>4</v>
+      </c>
+      <c r="C65">
+        <v>2</v>
+      </c>
+      <c r="D65" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E65">
+        <v>3633</v>
+      </c>
+      <c r="F65">
+        <v>16</v>
+      </c>
+      <c r="G65">
+        <v>2</v>
+      </c>
+      <c r="H65">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>2541</v>
+      </c>
+      <c r="B66">
+        <v>4</v>
+      </c>
+      <c r="C66">
+        <v>3</v>
+      </c>
+      <c r="D66" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E66">
+        <v>3649</v>
+      </c>
+      <c r="F66">
+        <v>16</v>
+      </c>
+      <c r="G66">
+        <v>1</v>
+      </c>
+      <c r="H66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>2545</v>
+      </c>
+      <c r="B67">
+        <v>4</v>
+      </c>
+      <c r="C67">
+        <v>2</v>
+      </c>
+      <c r="D67">
+        <f t="shared" ref="D67:D130" si="1">IF(ISNUMBER(VLOOKUP(A67, $E:$E, 1, FALSE)), 1, "")</f>
+        <v>1</v>
+      </c>
+      <c r="E67">
+        <v>3665</v>
+      </c>
+      <c r="F67">
+        <v>16</v>
+      </c>
+      <c r="G67">
+        <v>2</v>
+      </c>
+      <c r="H67">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>2549</v>
+      </c>
+      <c r="B68">
+        <v>4</v>
+      </c>
+      <c r="C68">
+        <v>3</v>
+      </c>
+      <c r="D68" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="E68">
+        <v>3681</v>
+      </c>
+      <c r="F68">
+        <v>32</v>
+      </c>
+      <c r="G68">
+        <v>2</v>
+      </c>
+      <c r="H68">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>2553</v>
+      </c>
+      <c r="B69">
+        <v>8</v>
+      </c>
+      <c r="C69">
+        <v>1</v>
+      </c>
+      <c r="D69" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="E69">
+        <v>3713</v>
+      </c>
+      <c r="F69">
+        <v>128</v>
+      </c>
+      <c r="G69">
+        <v>2</v>
+      </c>
+      <c r="H69">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>2561</v>
+      </c>
+      <c r="B70">
+        <v>64</v>
+      </c>
+      <c r="C70">
+        <v>-1</v>
+      </c>
+      <c r="D70">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="E70">
+        <v>3841</v>
+      </c>
+      <c r="F70">
+        <v>256</v>
+      </c>
+      <c r="G70">
+        <v>2</v>
+      </c>
+      <c r="H70">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>2625</v>
+      </c>
+      <c r="B71">
+        <v>32</v>
+      </c>
+      <c r="C71">
+        <v>-1</v>
+      </c>
+      <c r="D71" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>2657</v>
+      </c>
+      <c r="B72">
+        <v>16</v>
+      </c>
+      <c r="C72">
+        <v>-1</v>
+      </c>
+      <c r="D72" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>2673</v>
+      </c>
+      <c r="B73">
+        <v>8</v>
+      </c>
+      <c r="C73">
+        <v>-1</v>
+      </c>
+      <c r="D73" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>2681</v>
+      </c>
+      <c r="B74">
+        <v>4</v>
+      </c>
+      <c r="C74">
+        <v>-1</v>
+      </c>
+      <c r="D74" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>2685</v>
+      </c>
+      <c r="B75">
+        <v>4</v>
+      </c>
+      <c r="C75">
+        <v>4</v>
+      </c>
+      <c r="D75" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>2689</v>
+      </c>
+      <c r="B76">
+        <v>32</v>
+      </c>
+      <c r="C76">
+        <v>-1</v>
+      </c>
+      <c r="D76">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>2721</v>
+      </c>
+      <c r="B77">
+        <v>16</v>
+      </c>
+      <c r="C77">
+        <v>-1</v>
+      </c>
+      <c r="D77" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>2737</v>
+      </c>
+      <c r="B78">
+        <v>8</v>
+      </c>
+      <c r="C78">
+        <v>2</v>
+      </c>
+      <c r="D78" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>2745</v>
+      </c>
+      <c r="B79">
+        <v>4</v>
+      </c>
+      <c r="C79">
+        <v>2</v>
+      </c>
+      <c r="D79" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>2749</v>
+      </c>
+      <c r="B80">
+        <v>4</v>
+      </c>
+      <c r="C80">
+        <v>3</v>
+      </c>
+      <c r="D80" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>2753</v>
+      </c>
+      <c r="B81">
+        <v>16</v>
+      </c>
+      <c r="C81">
+        <v>2</v>
+      </c>
+      <c r="D81">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>2769</v>
+      </c>
+      <c r="B82">
+        <v>8</v>
+      </c>
+      <c r="C82">
+        <v>2</v>
+      </c>
+      <c r="D82" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>2777</v>
+      </c>
+      <c r="B83">
+        <v>4</v>
+      </c>
+      <c r="C83">
+        <v>2</v>
+      </c>
+      <c r="D83" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>2781</v>
+      </c>
+      <c r="B84">
+        <v>4</v>
+      </c>
+      <c r="C84">
+        <v>3</v>
+      </c>
+      <c r="D84" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>2785</v>
+      </c>
+      <c r="B85">
+        <v>8</v>
+      </c>
+      <c r="C85">
+        <v>2</v>
+      </c>
+      <c r="D85">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>2793</v>
+      </c>
+      <c r="B86">
+        <v>8</v>
+      </c>
+      <c r="C86">
+        <v>4</v>
+      </c>
+      <c r="D86">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>2801</v>
+      </c>
+      <c r="B87">
+        <v>16</v>
+      </c>
+      <c r="C87">
+        <v>3</v>
+      </c>
+      <c r="D87">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>2817</v>
+      </c>
+      <c r="B88">
+        <v>32</v>
+      </c>
+      <c r="C88">
+        <v>2</v>
+      </c>
+      <c r="D88">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>2849</v>
+      </c>
+      <c r="B89">
+        <v>16</v>
+      </c>
+      <c r="C89">
+        <v>2</v>
+      </c>
+      <c r="D89" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>2865</v>
+      </c>
+      <c r="B90">
+        <v>8</v>
+      </c>
+      <c r="C90">
+        <v>2</v>
+      </c>
+      <c r="D90" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>2873</v>
+      </c>
+      <c r="B91">
+        <v>4</v>
+      </c>
+      <c r="C91">
+        <v>2</v>
+      </c>
+      <c r="D91" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>2877</v>
+      </c>
+      <c r="B92">
+        <v>4</v>
+      </c>
+      <c r="C92">
+        <v>1</v>
+      </c>
+      <c r="D92" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>2881</v>
+      </c>
+      <c r="B93">
+        <v>16</v>
+      </c>
+      <c r="C93">
+        <v>2</v>
+      </c>
+      <c r="D93">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>2897</v>
+      </c>
+      <c r="B94">
+        <v>4</v>
+      </c>
+      <c r="C94">
+        <v>-1</v>
+      </c>
+      <c r="D94">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>2901</v>
+      </c>
+      <c r="B95">
+        <v>4</v>
+      </c>
+      <c r="C95">
+        <v>4</v>
+      </c>
+      <c r="D95" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>2905</v>
+      </c>
+      <c r="B96">
+        <v>8</v>
+      </c>
+      <c r="C96">
+        <v>3</v>
+      </c>
+      <c r="D96">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>2913</v>
+      </c>
+      <c r="B97">
+        <v>4</v>
+      </c>
+      <c r="C97">
+        <v>-1</v>
+      </c>
+      <c r="D97">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>2917</v>
+      </c>
+      <c r="B98">
+        <v>4</v>
+      </c>
+      <c r="C98">
+        <v>3</v>
+      </c>
+      <c r="D98" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>2921</v>
+      </c>
+      <c r="B99">
+        <v>8</v>
+      </c>
+      <c r="C99">
+        <v>3</v>
+      </c>
+      <c r="D99" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>2929</v>
+      </c>
+      <c r="B100">
+        <v>16</v>
+      </c>
+      <c r="C100">
+        <v>3</v>
+      </c>
+      <c r="D100" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>2945</v>
+      </c>
+      <c r="B101">
+        <v>8</v>
+      </c>
+      <c r="C101">
+        <v>-1</v>
+      </c>
+      <c r="D101">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>2953</v>
+      </c>
+      <c r="B102">
+        <v>4</v>
+      </c>
+      <c r="C102">
+        <v>2</v>
+      </c>
+      <c r="D102" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>2957</v>
+      </c>
+      <c r="B103">
+        <v>4</v>
+      </c>
+      <c r="C103">
+        <v>3</v>
+      </c>
+      <c r="D103" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>2961</v>
+      </c>
+      <c r="B104">
+        <v>4</v>
+      </c>
+      <c r="C104">
+        <v>2</v>
+      </c>
+      <c r="D104">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>2965</v>
+      </c>
+      <c r="B105">
+        <v>4</v>
+      </c>
+      <c r="C105">
+        <v>3</v>
+      </c>
+      <c r="D105" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>2969</v>
+      </c>
+      <c r="B106">
+        <v>8</v>
+      </c>
+      <c r="C106">
+        <v>3</v>
+      </c>
+      <c r="D106" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>2977</v>
+      </c>
+      <c r="B107">
+        <v>4</v>
+      </c>
+      <c r="C107">
+        <v>2</v>
+      </c>
+      <c r="D107">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>2981</v>
+      </c>
+      <c r="B108">
+        <v>4</v>
+      </c>
+      <c r="C108">
+        <v>3</v>
+      </c>
+      <c r="D108" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>2985</v>
+      </c>
+      <c r="B109">
+        <v>8</v>
+      </c>
+      <c r="C109">
+        <v>3</v>
+      </c>
+      <c r="D109" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>2993</v>
+      </c>
+      <c r="B110">
+        <v>16</v>
+      </c>
+      <c r="C110">
+        <v>1</v>
+      </c>
+      <c r="D110" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>3009</v>
+      </c>
+      <c r="B111">
+        <v>4</v>
+      </c>
+      <c r="C111">
+        <v>2</v>
+      </c>
+      <c r="D111">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>3013</v>
+      </c>
+      <c r="B112">
+        <v>4</v>
+      </c>
+      <c r="C112">
+        <v>1</v>
+      </c>
+      <c r="D112" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>3017</v>
+      </c>
+      <c r="B113">
+        <v>8</v>
+      </c>
+      <c r="C113">
+        <v>1</v>
+      </c>
+      <c r="D113" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>3025</v>
+      </c>
+      <c r="B114">
+        <v>16</v>
+      </c>
+      <c r="C114">
+        <v>1</v>
+      </c>
+      <c r="D114" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>3041</v>
+      </c>
+      <c r="B115">
+        <v>32</v>
+      </c>
+      <c r="C115">
+        <v>1</v>
+      </c>
+      <c r="D115" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>3073</v>
+      </c>
+      <c r="B116">
+        <v>64</v>
+      </c>
+      <c r="C116">
+        <v>-1</v>
+      </c>
+      <c r="D116">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>3137</v>
+      </c>
+      <c r="B117">
+        <v>32</v>
+      </c>
+      <c r="C117">
+        <v>2</v>
+      </c>
+      <c r="D117" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>3169</v>
+      </c>
+      <c r="B118">
+        <v>16</v>
+      </c>
+      <c r="C118">
+        <v>2</v>
+      </c>
+      <c r="D118" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>3185</v>
+      </c>
+      <c r="B119">
+        <v>8</v>
+      </c>
+      <c r="C119">
+        <v>2</v>
+      </c>
+      <c r="D119" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>3193</v>
+      </c>
+      <c r="B120">
+        <v>4</v>
+      </c>
+      <c r="C120">
+        <v>2</v>
+      </c>
+      <c r="D120" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>3197</v>
+      </c>
+      <c r="B121">
+        <v>4</v>
+      </c>
+      <c r="C121">
+        <v>3</v>
+      </c>
+      <c r="D121" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>3201</v>
+      </c>
+      <c r="B122">
+        <v>32</v>
+      </c>
+      <c r="C122">
+        <v>2</v>
+      </c>
+      <c r="D122">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>3233</v>
+      </c>
+      <c r="B123">
+        <v>16</v>
+      </c>
+      <c r="C123">
+        <v>2</v>
+      </c>
+      <c r="D123">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>3249</v>
+      </c>
+      <c r="B124">
+        <v>8</v>
+      </c>
+      <c r="C124">
+        <v>2</v>
+      </c>
+      <c r="D124">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>3257</v>
+      </c>
+      <c r="B125">
+        <v>8</v>
+      </c>
+      <c r="C125">
+        <v>4</v>
+      </c>
+      <c r="D125">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>3265</v>
+      </c>
+      <c r="B126">
+        <v>8</v>
+      </c>
+      <c r="C126">
+        <v>-1</v>
+      </c>
+      <c r="D126">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>3273</v>
+      </c>
+      <c r="B127">
+        <v>4</v>
+      </c>
+      <c r="C127">
+        <v>-1</v>
+      </c>
+      <c r="D127" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>3277</v>
+      </c>
+      <c r="B128">
+        <v>4</v>
+      </c>
+      <c r="C128">
+        <v>4</v>
+      </c>
+      <c r="D128" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>3281</v>
+      </c>
+      <c r="B129">
+        <v>4</v>
+      </c>
+      <c r="C129">
+        <v>-1</v>
+      </c>
+      <c r="D129">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>3285</v>
+      </c>
+      <c r="B130">
+        <v>4</v>
+      </c>
+      <c r="C130">
+        <v>3</v>
+      </c>
+      <c r="D130" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>3289</v>
+      </c>
+      <c r="B131">
+        <v>8</v>
+      </c>
+      <c r="C131">
+        <v>3</v>
+      </c>
+      <c r="D131" t="str">
+        <f t="shared" ref="D131:D186" si="2">IF(ISNUMBER(VLOOKUP(A131, $E:$E, 1, FALSE)), 1, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>3297</v>
+      </c>
+      <c r="B132">
+        <v>4</v>
+      </c>
+      <c r="C132">
+        <v>2</v>
+      </c>
+      <c r="D132">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>3301</v>
+      </c>
+      <c r="B133">
+        <v>4</v>
+      </c>
+      <c r="C133">
+        <v>3</v>
+      </c>
+      <c r="D133" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>3305</v>
+      </c>
+      <c r="B134">
+        <v>8</v>
+      </c>
+      <c r="C134">
+        <v>3</v>
+      </c>
+      <c r="D134" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>3313</v>
+      </c>
+      <c r="B135">
+        <v>16</v>
+      </c>
+      <c r="C135">
+        <v>1</v>
+      </c>
+      <c r="D135" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>3329</v>
+      </c>
+      <c r="B136">
+        <v>32</v>
+      </c>
+      <c r="C136">
+        <v>2</v>
+      </c>
+      <c r="D136">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>3361</v>
+      </c>
+      <c r="B137">
+        <v>8</v>
+      </c>
+      <c r="C137">
+        <v>-1</v>
+      </c>
+      <c r="D137">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>3369</v>
+      </c>
+      <c r="B138">
+        <v>4</v>
+      </c>
+      <c r="C138">
+        <v>-1</v>
+      </c>
+      <c r="D138" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>3373</v>
+      </c>
+      <c r="B139">
+        <v>4</v>
+      </c>
+      <c r="C139">
+        <v>3</v>
+      </c>
+      <c r="D139" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>3377</v>
+      </c>
+      <c r="B140">
+        <v>4</v>
+      </c>
+      <c r="C140">
+        <v>2</v>
+      </c>
+      <c r="D140">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>3381</v>
+      </c>
+      <c r="B141">
+        <v>4</v>
+      </c>
+      <c r="C141">
+        <v>3</v>
+      </c>
+      <c r="D141" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>3385</v>
+      </c>
+      <c r="B142">
+        <v>8</v>
+      </c>
+      <c r="C142">
+        <v>3</v>
+      </c>
+      <c r="D142" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>3393</v>
+      </c>
+      <c r="B143">
+        <v>8</v>
+      </c>
+      <c r="C143">
+        <v>2</v>
+      </c>
+      <c r="D143">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>3401</v>
+      </c>
+      <c r="B144">
+        <v>4</v>
+      </c>
+      <c r="C144">
+        <v>2</v>
+      </c>
+      <c r="D144" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>3405</v>
+      </c>
+      <c r="B145">
+        <v>4</v>
+      </c>
+      <c r="C145">
+        <v>3</v>
+      </c>
+      <c r="D145" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>3409</v>
+      </c>
+      <c r="B146">
+        <v>4</v>
+      </c>
+      <c r="C146">
+        <v>2</v>
+      </c>
+      <c r="D146">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>3413</v>
+      </c>
+      <c r="B147">
+        <v>4</v>
+      </c>
+      <c r="C147">
+        <v>3</v>
+      </c>
+      <c r="D147" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>3417</v>
+      </c>
+      <c r="B148">
+        <v>8</v>
+      </c>
+      <c r="C148">
+        <v>3</v>
+      </c>
+      <c r="D148" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>3425</v>
+      </c>
+      <c r="B149">
+        <v>4</v>
+      </c>
+      <c r="C149">
+        <v>2</v>
+      </c>
+      <c r="D149">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>3429</v>
+      </c>
+      <c r="B150">
+        <v>4</v>
+      </c>
+      <c r="C150">
+        <v>1</v>
+      </c>
+      <c r="D150" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>3433</v>
+      </c>
+      <c r="B151">
+        <v>8</v>
+      </c>
+      <c r="C151">
+        <v>1</v>
+      </c>
+      <c r="D151" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>3441</v>
+      </c>
+      <c r="B152">
+        <v>16</v>
+      </c>
+      <c r="C152">
+        <v>1</v>
+      </c>
+      <c r="D152" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>3457</v>
+      </c>
+      <c r="B153">
+        <v>8</v>
+      </c>
+      <c r="C153">
+        <v>2</v>
+      </c>
+      <c r="D153">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>3465</v>
+      </c>
+      <c r="B154">
+        <v>4</v>
+      </c>
+      <c r="C154">
+        <v>2</v>
+      </c>
+      <c r="D154" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>3469</v>
+      </c>
+      <c r="B155">
+        <v>4</v>
+      </c>
+      <c r="C155">
+        <v>3</v>
+      </c>
+      <c r="D155" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>3473</v>
+      </c>
+      <c r="B156">
+        <v>16</v>
+      </c>
+      <c r="C156">
+        <v>4</v>
+      </c>
+      <c r="D156">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>3489</v>
+      </c>
+      <c r="B157">
+        <v>32</v>
+      </c>
+      <c r="C157">
+        <v>3</v>
+      </c>
+      <c r="D157">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <v>3521</v>
+      </c>
+      <c r="B158">
+        <v>64</v>
+      </c>
+      <c r="C158">
+        <v>3</v>
+      </c>
+      <c r="D158">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A159">
+        <v>3585</v>
+      </c>
+      <c r="B159">
+        <v>16</v>
+      </c>
+      <c r="C159">
+        <v>-1</v>
+      </c>
+      <c r="D159">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A160">
+        <v>3601</v>
+      </c>
+      <c r="B160">
+        <v>8</v>
+      </c>
+      <c r="C160">
+        <v>2</v>
+      </c>
+      <c r="D160" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <v>3609</v>
+      </c>
+      <c r="B161">
+        <v>4</v>
+      </c>
+      <c r="C161">
+        <v>2</v>
+      </c>
+      <c r="D161" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>3613</v>
+      </c>
+      <c r="B162">
+        <v>4</v>
+      </c>
+      <c r="C162">
+        <v>3</v>
+      </c>
+      <c r="D162" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A163">
+        <v>3617</v>
+      </c>
+      <c r="B163">
+        <v>8</v>
+      </c>
+      <c r="C163">
+        <v>2</v>
+      </c>
+      <c r="D163">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A164">
+        <v>3625</v>
+      </c>
+      <c r="B164">
+        <v>4</v>
+      </c>
+      <c r="C164">
+        <v>2</v>
+      </c>
+      <c r="D164" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A165">
+        <v>3629</v>
+      </c>
+      <c r="B165">
+        <v>4</v>
+      </c>
+      <c r="C165">
+        <v>3</v>
+      </c>
+      <c r="D165" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <v>3633</v>
+      </c>
+      <c r="B166">
+        <v>4</v>
+      </c>
+      <c r="C166">
+        <v>2</v>
+      </c>
+      <c r="D166">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A167">
+        <v>3637</v>
+      </c>
+      <c r="B167">
+        <v>4</v>
+      </c>
+      <c r="C167">
+        <v>1</v>
+      </c>
+      <c r="D167" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>3641</v>
+      </c>
+      <c r="B168">
+        <v>8</v>
+      </c>
+      <c r="C168">
+        <v>1</v>
+      </c>
+      <c r="D168" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>3649</v>
+      </c>
+      <c r="B169">
+        <v>8</v>
+      </c>
+      <c r="C169">
+        <v>2</v>
+      </c>
+      <c r="D169">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>3657</v>
+      </c>
+      <c r="B170">
+        <v>4</v>
+      </c>
+      <c r="C170">
+        <v>2</v>
+      </c>
+      <c r="D170" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>3661</v>
+      </c>
+      <c r="B171">
+        <v>4</v>
+      </c>
+      <c r="C171">
+        <v>1</v>
+      </c>
+      <c r="D171" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>3665</v>
+      </c>
+      <c r="B172">
+        <v>16</v>
+      </c>
+      <c r="C172">
+        <v>3</v>
+      </c>
+      <c r="D172">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>3681</v>
+      </c>
+      <c r="B173">
+        <v>32</v>
+      </c>
+      <c r="C173">
+        <v>3</v>
+      </c>
+      <c r="D173">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>3713</v>
+      </c>
+      <c r="B174">
+        <v>4</v>
+      </c>
+      <c r="C174">
+        <v>-1</v>
+      </c>
+      <c r="D174">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>3717</v>
+      </c>
+      <c r="B175">
+        <v>4</v>
+      </c>
+      <c r="C175">
+        <v>3</v>
+      </c>
+      <c r="D175" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>3721</v>
+      </c>
+      <c r="B176">
+        <v>8</v>
+      </c>
+      <c r="C176">
+        <v>3</v>
+      </c>
+      <c r="D176" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>3729</v>
+      </c>
+      <c r="B177">
+        <v>16</v>
+      </c>
+      <c r="C177">
+        <v>3</v>
+      </c>
+      <c r="D177" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>3745</v>
+      </c>
+      <c r="B178">
+        <v>32</v>
+      </c>
+      <c r="C178">
+        <v>3</v>
+      </c>
+      <c r="D178" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <v>3777</v>
+      </c>
+      <c r="B179">
+        <v>64</v>
+      </c>
+      <c r="C179">
+        <v>3</v>
+      </c>
+      <c r="D179" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A180">
+        <v>3841</v>
+      </c>
+      <c r="B180">
+        <v>4</v>
+      </c>
+      <c r="C180">
+        <v>2</v>
+      </c>
+      <c r="D180">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <v>3845</v>
+      </c>
+      <c r="B181">
+        <v>4</v>
+      </c>
+      <c r="C181">
+        <v>3</v>
+      </c>
+      <c r="D181" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A182">
+        <v>3849</v>
+      </c>
+      <c r="B182">
+        <v>8</v>
+      </c>
+      <c r="C182">
+        <v>3</v>
+      </c>
+      <c r="D182" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A183">
+        <v>3857</v>
+      </c>
+      <c r="B183">
+        <v>16</v>
+      </c>
+      <c r="C183">
+        <v>3</v>
+      </c>
+      <c r="D183" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A184">
+        <v>3873</v>
+      </c>
+      <c r="B184">
+        <v>32</v>
+      </c>
+      <c r="C184">
+        <v>1</v>
+      </c>
+      <c r="D184" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A185">
+        <v>3905</v>
+      </c>
+      <c r="B185">
+        <v>64</v>
+      </c>
+      <c r="C185">
+        <v>1</v>
+      </c>
+      <c r="D185" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A186">
+        <v>3969</v>
+      </c>
+      <c r="B186">
+        <v>128</v>
+      </c>
+      <c r="C186">
+        <v>1</v>
+      </c>
+      <c r="D186" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/matlab/POLAR_SR_HR/node_struct.xlsx
+++ b/matlab/POLAR_SR_HR/node_struct.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\dev\polar_dev\matlab\POLAR_SR_HR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86355DDB-9055-461F-84C8-F088DA6D7886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AA9D3CD-BCA7-4418-92DB-51A736DBDB50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2700" yWindow="2580" windowWidth="23040" windowHeight="12108" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5760" yWindow="1668" windowWidth="23040" windowHeight="12108" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1|2" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="1|4" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
+    <sheet name="1|4" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -593,7 +594,7 @@
         <v>-1</v>
       </c>
       <c r="D3" t="str">
-        <f t="shared" ref="D2:D67" si="0">IF(ISNUMBER(VLOOKUP(A3, $E:$E, 1, FALSE)), 1, "")</f>
+        <f t="shared" ref="D3:D67" si="0">IF(ISNUMBER(VLOOKUP(A3, $E:$E, 1, FALSE)), 1, "")</f>
         <v/>
       </c>
       <c r="E3">
@@ -6873,6 +6874,2887 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38E5540C-9378-45B4-A7CA-F39AABBE151E}">
+  <dimension ref="A1:D205"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1">
+        <v>1</v>
+      </c>
+      <c r="B1">
+        <v>256</v>
+      </c>
+      <c r="C1">
+        <v>1</v>
+      </c>
+      <c r="D1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>257</v>
+      </c>
+      <c r="B2">
+        <v>128</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>385</v>
+      </c>
+      <c r="B3">
+        <v>64</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>449</v>
+      </c>
+      <c r="B4">
+        <v>32</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>481</v>
+      </c>
+      <c r="B5">
+        <v>16</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>497</v>
+      </c>
+      <c r="B6">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>505</v>
+      </c>
+      <c r="B7">
+        <v>8</v>
+      </c>
+      <c r="C7">
+        <v>-1</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>513</v>
+      </c>
+      <c r="B8">
+        <v>128</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>641</v>
+      </c>
+      <c r="B9">
+        <v>64</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>705</v>
+      </c>
+      <c r="B10">
+        <v>32</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>737</v>
+      </c>
+      <c r="B11">
+        <v>8</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>745</v>
+      </c>
+      <c r="B12">
+        <v>4</v>
+      </c>
+      <c r="C12">
+        <v>-1</v>
+      </c>
+      <c r="D12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>749</v>
+      </c>
+      <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13">
+        <v>-1</v>
+      </c>
+      <c r="D13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>753</v>
+      </c>
+      <c r="B14">
+        <v>4</v>
+      </c>
+      <c r="C14">
+        <v>-1</v>
+      </c>
+      <c r="D14">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>757</v>
+      </c>
+      <c r="B15">
+        <v>4</v>
+      </c>
+      <c r="C15">
+        <v>-1</v>
+      </c>
+      <c r="D15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>761</v>
+      </c>
+      <c r="B16">
+        <v>8</v>
+      </c>
+      <c r="C16">
+        <v>-1</v>
+      </c>
+      <c r="D16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>769</v>
+      </c>
+      <c r="B17">
+        <v>32</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>801</v>
+      </c>
+      <c r="B18">
+        <v>16</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>817</v>
+      </c>
+      <c r="B19">
+        <v>8</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>825</v>
+      </c>
+      <c r="B20">
+        <v>4</v>
+      </c>
+      <c r="C20">
+        <v>-1</v>
+      </c>
+      <c r="D20">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>829</v>
+      </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21">
+        <v>-1</v>
+      </c>
+      <c r="D21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>833</v>
+      </c>
+      <c r="B22">
+        <v>16</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>849</v>
+      </c>
+      <c r="B23">
+        <v>8</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>857</v>
+      </c>
+      <c r="B24">
+        <v>4</v>
+      </c>
+      <c r="C24">
+        <v>-1</v>
+      </c>
+      <c r="D24">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>861</v>
+      </c>
+      <c r="B25">
+        <v>4</v>
+      </c>
+      <c r="C25">
+        <v>-1</v>
+      </c>
+      <c r="D25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>865</v>
+      </c>
+      <c r="B26">
+        <v>8</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>873</v>
+      </c>
+      <c r="B27">
+        <v>4</v>
+      </c>
+      <c r="C27">
+        <v>-1</v>
+      </c>
+      <c r="D27">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>877</v>
+      </c>
+      <c r="B28">
+        <v>4</v>
+      </c>
+      <c r="C28">
+        <v>-1</v>
+      </c>
+      <c r="D28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>881</v>
+      </c>
+      <c r="B29">
+        <v>4</v>
+      </c>
+      <c r="C29">
+        <v>-1</v>
+      </c>
+      <c r="D29">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>885</v>
+      </c>
+      <c r="B30">
+        <v>4</v>
+      </c>
+      <c r="C30">
+        <v>-1</v>
+      </c>
+      <c r="D30">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>889</v>
+      </c>
+      <c r="B31">
+        <v>8</v>
+      </c>
+      <c r="C31">
+        <v>-1</v>
+      </c>
+      <c r="D31">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>897</v>
+      </c>
+      <c r="B32">
+        <v>16</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>913</v>
+      </c>
+      <c r="B33">
+        <v>8</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>921</v>
+      </c>
+      <c r="B34">
+        <v>4</v>
+      </c>
+      <c r="C34">
+        <v>-1</v>
+      </c>
+      <c r="D34">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>925</v>
+      </c>
+      <c r="B35">
+        <v>4</v>
+      </c>
+      <c r="C35">
+        <v>-1</v>
+      </c>
+      <c r="D35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>929</v>
+      </c>
+      <c r="B36">
+        <v>8</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+      <c r="D36">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>937</v>
+      </c>
+      <c r="B37">
+        <v>8</v>
+      </c>
+      <c r="C37">
+        <v>-1</v>
+      </c>
+      <c r="D37">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>945</v>
+      </c>
+      <c r="B38">
+        <v>16</v>
+      </c>
+      <c r="C38">
+        <v>-1</v>
+      </c>
+      <c r="D38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>961</v>
+      </c>
+      <c r="B39">
+        <v>4</v>
+      </c>
+      <c r="C39">
+        <v>-1</v>
+      </c>
+      <c r="D39">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>965</v>
+      </c>
+      <c r="B40">
+        <v>4</v>
+      </c>
+      <c r="C40">
+        <v>-1</v>
+      </c>
+      <c r="D40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>969</v>
+      </c>
+      <c r="B41">
+        <v>8</v>
+      </c>
+      <c r="C41">
+        <v>-1</v>
+      </c>
+      <c r="D41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>977</v>
+      </c>
+      <c r="B42">
+        <v>16</v>
+      </c>
+      <c r="C42">
+        <v>-1</v>
+      </c>
+      <c r="D42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>993</v>
+      </c>
+      <c r="B43">
+        <v>32</v>
+      </c>
+      <c r="C43">
+        <v>-1</v>
+      </c>
+      <c r="D43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>1025</v>
+      </c>
+      <c r="B44">
+        <v>64</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+      <c r="D44">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>1089</v>
+      </c>
+      <c r="B45">
+        <v>32</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+      <c r="D45">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>1121</v>
+      </c>
+      <c r="B46">
+        <v>16</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+      <c r="D46">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>1137</v>
+      </c>
+      <c r="B47">
+        <v>8</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+      <c r="D47">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>1145</v>
+      </c>
+      <c r="B48">
+        <v>4</v>
+      </c>
+      <c r="C48">
+        <v>-1</v>
+      </c>
+      <c r="D48">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>1149</v>
+      </c>
+      <c r="B49">
+        <v>4</v>
+      </c>
+      <c r="C49">
+        <v>-1</v>
+      </c>
+      <c r="D49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>1153</v>
+      </c>
+      <c r="B50">
+        <v>32</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+      <c r="D50">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>1185</v>
+      </c>
+      <c r="B51">
+        <v>16</v>
+      </c>
+      <c r="C51">
+        <v>1</v>
+      </c>
+      <c r="D51">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>1201</v>
+      </c>
+      <c r="B52">
+        <v>8</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+      <c r="D52">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>1209</v>
+      </c>
+      <c r="B53">
+        <v>4</v>
+      </c>
+      <c r="C53">
+        <v>-1</v>
+      </c>
+      <c r="D53">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>1213</v>
+      </c>
+      <c r="B54">
+        <v>4</v>
+      </c>
+      <c r="C54">
+        <v>-1</v>
+      </c>
+      <c r="D54">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>1217</v>
+      </c>
+      <c r="B55">
+        <v>16</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
+      <c r="D55">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>1233</v>
+      </c>
+      <c r="B56">
+        <v>8</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
+      <c r="D56">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>1241</v>
+      </c>
+      <c r="B57">
+        <v>4</v>
+      </c>
+      <c r="C57">
+        <v>-1</v>
+      </c>
+      <c r="D57">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>1245</v>
+      </c>
+      <c r="B58">
+        <v>4</v>
+      </c>
+      <c r="C58">
+        <v>-1</v>
+      </c>
+      <c r="D58">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>1249</v>
+      </c>
+      <c r="B59">
+        <v>8</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
+      <c r="D59">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>1257</v>
+      </c>
+      <c r="B60">
+        <v>4</v>
+      </c>
+      <c r="C60">
+        <v>-1</v>
+      </c>
+      <c r="D60">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>1261</v>
+      </c>
+      <c r="B61">
+        <v>4</v>
+      </c>
+      <c r="C61">
+        <v>-1</v>
+      </c>
+      <c r="D61">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>1265</v>
+      </c>
+      <c r="B62">
+        <v>16</v>
+      </c>
+      <c r="C62">
+        <v>-1</v>
+      </c>
+      <c r="D62">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>1281</v>
+      </c>
+      <c r="B63">
+        <v>32</v>
+      </c>
+      <c r="C63">
+        <v>1</v>
+      </c>
+      <c r="D63">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>1313</v>
+      </c>
+      <c r="B64">
+        <v>16</v>
+      </c>
+      <c r="C64">
+        <v>1</v>
+      </c>
+      <c r="D64">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>1329</v>
+      </c>
+      <c r="B65">
+        <v>8</v>
+      </c>
+      <c r="C65">
+        <v>1</v>
+      </c>
+      <c r="D65">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>1337</v>
+      </c>
+      <c r="B66">
+        <v>4</v>
+      </c>
+      <c r="C66">
+        <v>-1</v>
+      </c>
+      <c r="D66">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>1341</v>
+      </c>
+      <c r="B67">
+        <v>4</v>
+      </c>
+      <c r="C67">
+        <v>-1</v>
+      </c>
+      <c r="D67">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>1345</v>
+      </c>
+      <c r="B68">
+        <v>16</v>
+      </c>
+      <c r="C68">
+        <v>1</v>
+      </c>
+      <c r="D68">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>1361</v>
+      </c>
+      <c r="B69">
+        <v>8</v>
+      </c>
+      <c r="C69">
+        <v>1</v>
+      </c>
+      <c r="D69">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>1369</v>
+      </c>
+      <c r="B70">
+        <v>8</v>
+      </c>
+      <c r="C70">
+        <v>-1</v>
+      </c>
+      <c r="D70">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>1377</v>
+      </c>
+      <c r="B71">
+        <v>4</v>
+      </c>
+      <c r="C71">
+        <v>-1</v>
+      </c>
+      <c r="D71">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>1381</v>
+      </c>
+      <c r="B72">
+        <v>4</v>
+      </c>
+      <c r="C72">
+        <v>-1</v>
+      </c>
+      <c r="D72">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>1385</v>
+      </c>
+      <c r="B73">
+        <v>8</v>
+      </c>
+      <c r="C73">
+        <v>-1</v>
+      </c>
+      <c r="D73">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>1393</v>
+      </c>
+      <c r="B74">
+        <v>16</v>
+      </c>
+      <c r="C74">
+        <v>-1</v>
+      </c>
+      <c r="D74">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>1409</v>
+      </c>
+      <c r="B75">
+        <v>8</v>
+      </c>
+      <c r="C75">
+        <v>1</v>
+      </c>
+      <c r="D75">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>1417</v>
+      </c>
+      <c r="B76">
+        <v>4</v>
+      </c>
+      <c r="C76">
+        <v>-1</v>
+      </c>
+      <c r="D76">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>1421</v>
+      </c>
+      <c r="B77">
+        <v>4</v>
+      </c>
+      <c r="C77">
+        <v>-1</v>
+      </c>
+      <c r="D77">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>1425</v>
+      </c>
+      <c r="B78">
+        <v>4</v>
+      </c>
+      <c r="C78">
+        <v>-1</v>
+      </c>
+      <c r="D78">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>1429</v>
+      </c>
+      <c r="B79">
+        <v>4</v>
+      </c>
+      <c r="C79">
+        <v>-1</v>
+      </c>
+      <c r="D79">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>1433</v>
+      </c>
+      <c r="B80">
+        <v>8</v>
+      </c>
+      <c r="C80">
+        <v>-1</v>
+      </c>
+      <c r="D80">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>1441</v>
+      </c>
+      <c r="B81">
+        <v>4</v>
+      </c>
+      <c r="C81">
+        <v>-1</v>
+      </c>
+      <c r="D81">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>1445</v>
+      </c>
+      <c r="B82">
+        <v>4</v>
+      </c>
+      <c r="C82">
+        <v>-1</v>
+      </c>
+      <c r="D82">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>1449</v>
+      </c>
+      <c r="B83">
+        <v>8</v>
+      </c>
+      <c r="C83">
+        <v>-1</v>
+      </c>
+      <c r="D83">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>1457</v>
+      </c>
+      <c r="B84">
+        <v>16</v>
+      </c>
+      <c r="C84">
+        <v>-1</v>
+      </c>
+      <c r="D84">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>1473</v>
+      </c>
+      <c r="B85">
+        <v>4</v>
+      </c>
+      <c r="C85">
+        <v>-1</v>
+      </c>
+      <c r="D85">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>1477</v>
+      </c>
+      <c r="B86">
+        <v>4</v>
+      </c>
+      <c r="C86">
+        <v>-1</v>
+      </c>
+      <c r="D86">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>1481</v>
+      </c>
+      <c r="B87">
+        <v>8</v>
+      </c>
+      <c r="C87">
+        <v>-1</v>
+      </c>
+      <c r="D87">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>1489</v>
+      </c>
+      <c r="B88">
+        <v>16</v>
+      </c>
+      <c r="C88">
+        <v>-1</v>
+      </c>
+      <c r="D88">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>1505</v>
+      </c>
+      <c r="B89">
+        <v>32</v>
+      </c>
+      <c r="C89">
+        <v>-1</v>
+      </c>
+      <c r="D89">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>1537</v>
+      </c>
+      <c r="B90">
+        <v>32</v>
+      </c>
+      <c r="C90">
+        <v>1</v>
+      </c>
+      <c r="D90">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>1569</v>
+      </c>
+      <c r="B91">
+        <v>16</v>
+      </c>
+      <c r="C91">
+        <v>1</v>
+      </c>
+      <c r="D91">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>1585</v>
+      </c>
+      <c r="B92">
+        <v>4</v>
+      </c>
+      <c r="C92">
+        <v>-1</v>
+      </c>
+      <c r="D92">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>1589</v>
+      </c>
+      <c r="B93">
+        <v>4</v>
+      </c>
+      <c r="C93">
+        <v>-1</v>
+      </c>
+      <c r="D93">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>1593</v>
+      </c>
+      <c r="B94">
+        <v>8</v>
+      </c>
+      <c r="C94">
+        <v>-1</v>
+      </c>
+      <c r="D94">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>1601</v>
+      </c>
+      <c r="B95">
+        <v>8</v>
+      </c>
+      <c r="C95">
+        <v>1</v>
+      </c>
+      <c r="D95">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>1609</v>
+      </c>
+      <c r="B96">
+        <v>4</v>
+      </c>
+      <c r="C96">
+        <v>-1</v>
+      </c>
+      <c r="D96">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>1613</v>
+      </c>
+      <c r="B97">
+        <v>4</v>
+      </c>
+      <c r="C97">
+        <v>-1</v>
+      </c>
+      <c r="D97">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>1617</v>
+      </c>
+      <c r="B98">
+        <v>4</v>
+      </c>
+      <c r="C98">
+        <v>-1</v>
+      </c>
+      <c r="D98">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>1621</v>
+      </c>
+      <c r="B99">
+        <v>4</v>
+      </c>
+      <c r="C99">
+        <v>-1</v>
+      </c>
+      <c r="D99">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>1625</v>
+      </c>
+      <c r="B100">
+        <v>8</v>
+      </c>
+      <c r="C100">
+        <v>-1</v>
+      </c>
+      <c r="D100">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>1633</v>
+      </c>
+      <c r="B101">
+        <v>4</v>
+      </c>
+      <c r="C101">
+        <v>-1</v>
+      </c>
+      <c r="D101">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>1637</v>
+      </c>
+      <c r="B102">
+        <v>4</v>
+      </c>
+      <c r="C102">
+        <v>-1</v>
+      </c>
+      <c r="D102">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>1641</v>
+      </c>
+      <c r="B103">
+        <v>8</v>
+      </c>
+      <c r="C103">
+        <v>-1</v>
+      </c>
+      <c r="D103">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>1649</v>
+      </c>
+      <c r="B104">
+        <v>16</v>
+      </c>
+      <c r="C104">
+        <v>-1</v>
+      </c>
+      <c r="D104">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>1665</v>
+      </c>
+      <c r="B105">
+        <v>8</v>
+      </c>
+      <c r="C105">
+        <v>1</v>
+      </c>
+      <c r="D105">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>1673</v>
+      </c>
+      <c r="B106">
+        <v>4</v>
+      </c>
+      <c r="C106">
+        <v>-1</v>
+      </c>
+      <c r="D106">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>1677</v>
+      </c>
+      <c r="B107">
+        <v>4</v>
+      </c>
+      <c r="C107">
+        <v>-1</v>
+      </c>
+      <c r="D107">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>1681</v>
+      </c>
+      <c r="B108">
+        <v>4</v>
+      </c>
+      <c r="C108">
+        <v>-1</v>
+      </c>
+      <c r="D108">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>1685</v>
+      </c>
+      <c r="B109">
+        <v>4</v>
+      </c>
+      <c r="C109">
+        <v>-1</v>
+      </c>
+      <c r="D109">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>1689</v>
+      </c>
+      <c r="B110">
+        <v>8</v>
+      </c>
+      <c r="C110">
+        <v>-1</v>
+      </c>
+      <c r="D110">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>1697</v>
+      </c>
+      <c r="B111">
+        <v>32</v>
+      </c>
+      <c r="C111">
+        <v>-1</v>
+      </c>
+      <c r="D111">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>1729</v>
+      </c>
+      <c r="B112">
+        <v>64</v>
+      </c>
+      <c r="C112">
+        <v>-1</v>
+      </c>
+      <c r="D112">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>1793</v>
+      </c>
+      <c r="B113">
+        <v>8</v>
+      </c>
+      <c r="C113">
+        <v>1</v>
+      </c>
+      <c r="D113">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>1801</v>
+      </c>
+      <c r="B114">
+        <v>8</v>
+      </c>
+      <c r="C114">
+        <v>-1</v>
+      </c>
+      <c r="D114">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>1809</v>
+      </c>
+      <c r="B115">
+        <v>16</v>
+      </c>
+      <c r="C115">
+        <v>-1</v>
+      </c>
+      <c r="D115">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>1825</v>
+      </c>
+      <c r="B116">
+        <v>32</v>
+      </c>
+      <c r="C116">
+        <v>-1</v>
+      </c>
+      <c r="D116">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>1857</v>
+      </c>
+      <c r="B117">
+        <v>64</v>
+      </c>
+      <c r="C117">
+        <v>-1</v>
+      </c>
+      <c r="D117">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>1921</v>
+      </c>
+      <c r="B118">
+        <v>128</v>
+      </c>
+      <c r="C118">
+        <v>-1</v>
+      </c>
+      <c r="D118">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>2049</v>
+      </c>
+      <c r="B119">
+        <v>64</v>
+      </c>
+      <c r="C119">
+        <v>1</v>
+      </c>
+      <c r="D119">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>2113</v>
+      </c>
+      <c r="B120">
+        <v>32</v>
+      </c>
+      <c r="C120">
+        <v>1</v>
+      </c>
+      <c r="D120">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>2145</v>
+      </c>
+      <c r="B121">
+        <v>16</v>
+      </c>
+      <c r="C121">
+        <v>1</v>
+      </c>
+      <c r="D121">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>2161</v>
+      </c>
+      <c r="B122">
+        <v>8</v>
+      </c>
+      <c r="C122">
+        <v>1</v>
+      </c>
+      <c r="D122">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>2169</v>
+      </c>
+      <c r="B123">
+        <v>4</v>
+      </c>
+      <c r="C123">
+        <v>-1</v>
+      </c>
+      <c r="D123">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>2173</v>
+      </c>
+      <c r="B124">
+        <v>4</v>
+      </c>
+      <c r="C124">
+        <v>-1</v>
+      </c>
+      <c r="D124">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>2177</v>
+      </c>
+      <c r="B125">
+        <v>32</v>
+      </c>
+      <c r="C125">
+        <v>1</v>
+      </c>
+      <c r="D125">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>2209</v>
+      </c>
+      <c r="B126">
+        <v>16</v>
+      </c>
+      <c r="C126">
+        <v>1</v>
+      </c>
+      <c r="D126">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>2225</v>
+      </c>
+      <c r="B127">
+        <v>8</v>
+      </c>
+      <c r="C127">
+        <v>1</v>
+      </c>
+      <c r="D127">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>2233</v>
+      </c>
+      <c r="B128">
+        <v>8</v>
+      </c>
+      <c r="C128">
+        <v>-1</v>
+      </c>
+      <c r="D128">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>2241</v>
+      </c>
+      <c r="B129">
+        <v>16</v>
+      </c>
+      <c r="C129">
+        <v>1</v>
+      </c>
+      <c r="D129">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>2257</v>
+      </c>
+      <c r="B130">
+        <v>4</v>
+      </c>
+      <c r="C130">
+        <v>-1</v>
+      </c>
+      <c r="D130">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>2261</v>
+      </c>
+      <c r="B131">
+        <v>4</v>
+      </c>
+      <c r="C131">
+        <v>-1</v>
+      </c>
+      <c r="D131">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>2265</v>
+      </c>
+      <c r="B132">
+        <v>8</v>
+      </c>
+      <c r="C132">
+        <v>-1</v>
+      </c>
+      <c r="D132">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>2273</v>
+      </c>
+      <c r="B133">
+        <v>4</v>
+      </c>
+      <c r="C133">
+        <v>-1</v>
+      </c>
+      <c r="D133">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>2277</v>
+      </c>
+      <c r="B134">
+        <v>4</v>
+      </c>
+      <c r="C134">
+        <v>-1</v>
+      </c>
+      <c r="D134">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>2281</v>
+      </c>
+      <c r="B135">
+        <v>8</v>
+      </c>
+      <c r="C135">
+        <v>-1</v>
+      </c>
+      <c r="D135">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>2289</v>
+      </c>
+      <c r="B136">
+        <v>16</v>
+      </c>
+      <c r="C136">
+        <v>-1</v>
+      </c>
+      <c r="D136">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>2305</v>
+      </c>
+      <c r="B137">
+        <v>32</v>
+      </c>
+      <c r="C137">
+        <v>1</v>
+      </c>
+      <c r="D137">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>2337</v>
+      </c>
+      <c r="B138">
+        <v>8</v>
+      </c>
+      <c r="C138">
+        <v>1</v>
+      </c>
+      <c r="D138">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>2345</v>
+      </c>
+      <c r="B139">
+        <v>4</v>
+      </c>
+      <c r="C139">
+        <v>-1</v>
+      </c>
+      <c r="D139">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>2349</v>
+      </c>
+      <c r="B140">
+        <v>4</v>
+      </c>
+      <c r="C140">
+        <v>-1</v>
+      </c>
+      <c r="D140">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>2353</v>
+      </c>
+      <c r="B141">
+        <v>4</v>
+      </c>
+      <c r="C141">
+        <v>-1</v>
+      </c>
+      <c r="D141">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>2357</v>
+      </c>
+      <c r="B142">
+        <v>4</v>
+      </c>
+      <c r="C142">
+        <v>-1</v>
+      </c>
+      <c r="D142">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>2361</v>
+      </c>
+      <c r="B143">
+        <v>8</v>
+      </c>
+      <c r="C143">
+        <v>-1</v>
+      </c>
+      <c r="D143">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>2369</v>
+      </c>
+      <c r="B144">
+        <v>8</v>
+      </c>
+      <c r="C144">
+        <v>1</v>
+      </c>
+      <c r="D144">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>2377</v>
+      </c>
+      <c r="B145">
+        <v>4</v>
+      </c>
+      <c r="C145">
+        <v>-1</v>
+      </c>
+      <c r="D145">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>2381</v>
+      </c>
+      <c r="B146">
+        <v>4</v>
+      </c>
+      <c r="C146">
+        <v>-1</v>
+      </c>
+      <c r="D146">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>2385</v>
+      </c>
+      <c r="B147">
+        <v>4</v>
+      </c>
+      <c r="C147">
+        <v>-1</v>
+      </c>
+      <c r="D147">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>2389</v>
+      </c>
+      <c r="B148">
+        <v>4</v>
+      </c>
+      <c r="C148">
+        <v>-1</v>
+      </c>
+      <c r="D148">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>2393</v>
+      </c>
+      <c r="B149">
+        <v>8</v>
+      </c>
+      <c r="C149">
+        <v>-1</v>
+      </c>
+      <c r="D149">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>2401</v>
+      </c>
+      <c r="B150">
+        <v>4</v>
+      </c>
+      <c r="C150">
+        <v>-1</v>
+      </c>
+      <c r="D150">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>2405</v>
+      </c>
+      <c r="B151">
+        <v>4</v>
+      </c>
+      <c r="C151">
+        <v>-1</v>
+      </c>
+      <c r="D151">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>2409</v>
+      </c>
+      <c r="B152">
+        <v>8</v>
+      </c>
+      <c r="C152">
+        <v>-1</v>
+      </c>
+      <c r="D152">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>2417</v>
+      </c>
+      <c r="B153">
+        <v>16</v>
+      </c>
+      <c r="C153">
+        <v>-1</v>
+      </c>
+      <c r="D153">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>2433</v>
+      </c>
+      <c r="B154">
+        <v>8</v>
+      </c>
+      <c r="C154">
+        <v>1</v>
+      </c>
+      <c r="D154">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>2441</v>
+      </c>
+      <c r="B155">
+        <v>4</v>
+      </c>
+      <c r="C155">
+        <v>-1</v>
+      </c>
+      <c r="D155">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>2445</v>
+      </c>
+      <c r="B156">
+        <v>4</v>
+      </c>
+      <c r="C156">
+        <v>-1</v>
+      </c>
+      <c r="D156">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>2449</v>
+      </c>
+      <c r="B157">
+        <v>16</v>
+      </c>
+      <c r="C157">
+        <v>-1</v>
+      </c>
+      <c r="D157">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <v>2465</v>
+      </c>
+      <c r="B158">
+        <v>32</v>
+      </c>
+      <c r="C158">
+        <v>-1</v>
+      </c>
+      <c r="D158">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A159">
+        <v>2497</v>
+      </c>
+      <c r="B159">
+        <v>64</v>
+      </c>
+      <c r="C159">
+        <v>-1</v>
+      </c>
+      <c r="D159">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A160">
+        <v>2561</v>
+      </c>
+      <c r="B160">
+        <v>16</v>
+      </c>
+      <c r="C160">
+        <v>1</v>
+      </c>
+      <c r="D160">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <v>2577</v>
+      </c>
+      <c r="B161">
+        <v>8</v>
+      </c>
+      <c r="C161">
+        <v>1</v>
+      </c>
+      <c r="D161">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>2585</v>
+      </c>
+      <c r="B162">
+        <v>4</v>
+      </c>
+      <c r="C162">
+        <v>-1</v>
+      </c>
+      <c r="D162">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A163">
+        <v>2589</v>
+      </c>
+      <c r="B163">
+        <v>4</v>
+      </c>
+      <c r="C163">
+        <v>-1</v>
+      </c>
+      <c r="D163">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A164">
+        <v>2593</v>
+      </c>
+      <c r="B164">
+        <v>8</v>
+      </c>
+      <c r="C164">
+        <v>1</v>
+      </c>
+      <c r="D164">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A165">
+        <v>2601</v>
+      </c>
+      <c r="B165">
+        <v>4</v>
+      </c>
+      <c r="C165">
+        <v>-1</v>
+      </c>
+      <c r="D165">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <v>2605</v>
+      </c>
+      <c r="B166">
+        <v>4</v>
+      </c>
+      <c r="C166">
+        <v>-1</v>
+      </c>
+      <c r="D166">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A167">
+        <v>2609</v>
+      </c>
+      <c r="B167">
+        <v>4</v>
+      </c>
+      <c r="C167">
+        <v>-1</v>
+      </c>
+      <c r="D167">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>2613</v>
+      </c>
+      <c r="B168">
+        <v>4</v>
+      </c>
+      <c r="C168">
+        <v>-1</v>
+      </c>
+      <c r="D168">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>2617</v>
+      </c>
+      <c r="B169">
+        <v>8</v>
+      </c>
+      <c r="C169">
+        <v>-1</v>
+      </c>
+      <c r="D169">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>2625</v>
+      </c>
+      <c r="B170">
+        <v>8</v>
+      </c>
+      <c r="C170">
+        <v>1</v>
+      </c>
+      <c r="D170">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>2633</v>
+      </c>
+      <c r="B171">
+        <v>8</v>
+      </c>
+      <c r="C171">
+        <v>-1</v>
+      </c>
+      <c r="D171">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>2641</v>
+      </c>
+      <c r="B172">
+        <v>16</v>
+      </c>
+      <c r="C172">
+        <v>-1</v>
+      </c>
+      <c r="D172">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>2657</v>
+      </c>
+      <c r="B173">
+        <v>32</v>
+      </c>
+      <c r="C173">
+        <v>-1</v>
+      </c>
+      <c r="D173">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>2689</v>
+      </c>
+      <c r="B174">
+        <v>4</v>
+      </c>
+      <c r="C174">
+        <v>-1</v>
+      </c>
+      <c r="D174">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>2693</v>
+      </c>
+      <c r="B175">
+        <v>4</v>
+      </c>
+      <c r="C175">
+        <v>-1</v>
+      </c>
+      <c r="D175">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>2697</v>
+      </c>
+      <c r="B176">
+        <v>8</v>
+      </c>
+      <c r="C176">
+        <v>-1</v>
+      </c>
+      <c r="D176">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>2705</v>
+      </c>
+      <c r="B177">
+        <v>16</v>
+      </c>
+      <c r="C177">
+        <v>-1</v>
+      </c>
+      <c r="D177">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>2721</v>
+      </c>
+      <c r="B178">
+        <v>32</v>
+      </c>
+      <c r="C178">
+        <v>-1</v>
+      </c>
+      <c r="D178">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <v>2753</v>
+      </c>
+      <c r="B179">
+        <v>64</v>
+      </c>
+      <c r="C179">
+        <v>-1</v>
+      </c>
+      <c r="D179">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A180">
+        <v>2817</v>
+      </c>
+      <c r="B180">
+        <v>4</v>
+      </c>
+      <c r="C180">
+        <v>-1</v>
+      </c>
+      <c r="D180">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <v>2821</v>
+      </c>
+      <c r="B181">
+        <v>4</v>
+      </c>
+      <c r="C181">
+        <v>-1</v>
+      </c>
+      <c r="D181">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A182">
+        <v>2825</v>
+      </c>
+      <c r="B182">
+        <v>8</v>
+      </c>
+      <c r="C182">
+        <v>-1</v>
+      </c>
+      <c r="D182">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A183">
+        <v>2833</v>
+      </c>
+      <c r="B183">
+        <v>16</v>
+      </c>
+      <c r="C183">
+        <v>-1</v>
+      </c>
+      <c r="D183">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A184">
+        <v>2849</v>
+      </c>
+      <c r="B184">
+        <v>32</v>
+      </c>
+      <c r="C184">
+        <v>-1</v>
+      </c>
+      <c r="D184">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A185">
+        <v>2881</v>
+      </c>
+      <c r="B185">
+        <v>64</v>
+      </c>
+      <c r="C185">
+        <v>-1</v>
+      </c>
+      <c r="D185">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A186">
+        <v>2945</v>
+      </c>
+      <c r="B186">
+        <v>128</v>
+      </c>
+      <c r="C186">
+        <v>-1</v>
+      </c>
+      <c r="D186">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A187">
+        <v>3073</v>
+      </c>
+      <c r="B187">
+        <v>16</v>
+      </c>
+      <c r="C187">
+        <v>1</v>
+      </c>
+      <c r="D187">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A188">
+        <v>3089</v>
+      </c>
+      <c r="B188">
+        <v>8</v>
+      </c>
+      <c r="C188">
+        <v>1</v>
+      </c>
+      <c r="D188">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A189">
+        <v>3097</v>
+      </c>
+      <c r="B189">
+        <v>8</v>
+      </c>
+      <c r="C189">
+        <v>-1</v>
+      </c>
+      <c r="D189">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A190">
+        <v>3105</v>
+      </c>
+      <c r="B190">
+        <v>8</v>
+      </c>
+      <c r="C190">
+        <v>1</v>
+      </c>
+      <c r="D190">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A191">
+        <v>3113</v>
+      </c>
+      <c r="B191">
+        <v>8</v>
+      </c>
+      <c r="C191">
+        <v>-1</v>
+      </c>
+      <c r="D191">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A192">
+        <v>3121</v>
+      </c>
+      <c r="B192">
+        <v>16</v>
+      </c>
+      <c r="C192">
+        <v>-1</v>
+      </c>
+      <c r="D192">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A193">
+        <v>3137</v>
+      </c>
+      <c r="B193">
+        <v>4</v>
+      </c>
+      <c r="C193">
+        <v>-1</v>
+      </c>
+      <c r="D193">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A194">
+        <v>3141</v>
+      </c>
+      <c r="B194">
+        <v>4</v>
+      </c>
+      <c r="C194">
+        <v>-1</v>
+      </c>
+      <c r="D194">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A195">
+        <v>3145</v>
+      </c>
+      <c r="B195">
+        <v>8</v>
+      </c>
+      <c r="C195">
+        <v>-1</v>
+      </c>
+      <c r="D195">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A196">
+        <v>3153</v>
+      </c>
+      <c r="B196">
+        <v>16</v>
+      </c>
+      <c r="C196">
+        <v>-1</v>
+      </c>
+      <c r="D196">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A197">
+        <v>3169</v>
+      </c>
+      <c r="B197">
+        <v>32</v>
+      </c>
+      <c r="C197">
+        <v>-1</v>
+      </c>
+      <c r="D197">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A198">
+        <v>3201</v>
+      </c>
+      <c r="B198">
+        <v>4</v>
+      </c>
+      <c r="C198">
+        <v>-1</v>
+      </c>
+      <c r="D198">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A199">
+        <v>3205</v>
+      </c>
+      <c r="B199">
+        <v>4</v>
+      </c>
+      <c r="C199">
+        <v>-1</v>
+      </c>
+      <c r="D199">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A200">
+        <v>3209</v>
+      </c>
+      <c r="B200">
+        <v>8</v>
+      </c>
+      <c r="C200">
+        <v>-1</v>
+      </c>
+      <c r="D200">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A201">
+        <v>3217</v>
+      </c>
+      <c r="B201">
+        <v>16</v>
+      </c>
+      <c r="C201">
+        <v>-1</v>
+      </c>
+      <c r="D201">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A202">
+        <v>3233</v>
+      </c>
+      <c r="B202">
+        <v>32</v>
+      </c>
+      <c r="C202">
+        <v>-1</v>
+      </c>
+      <c r="D202">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A203">
+        <v>3265</v>
+      </c>
+      <c r="B203">
+        <v>64</v>
+      </c>
+      <c r="C203">
+        <v>-1</v>
+      </c>
+      <c r="D203">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A204">
+        <v>3329</v>
+      </c>
+      <c r="B204">
+        <v>256</v>
+      </c>
+      <c r="C204">
+        <v>-1</v>
+      </c>
+      <c r="D204">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A205">
+        <v>3585</v>
+      </c>
+      <c r="B205">
+        <v>512</v>
+      </c>
+      <c r="C205">
+        <v>-1</v>
+      </c>
+      <c r="D205">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8126B6E8-E062-4170-870C-DC6A28D2CB16}">
   <dimension ref="A1:P31"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
@@ -7548,7 +10430,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33F8C8D1-2097-4368-9F61-CF173B408D0C}">
   <dimension ref="A2:H186"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>

--- a/matlab/POLAR_SR_HR/node_struct.xlsx
+++ b/matlab/POLAR_SR_HR/node_struct.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\dev\polar_dev\matlab\POLAR_SR_HR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3531D231-6318-4AFA-A782-003F04E0C3BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{872203F4-2146-4204-B4D3-64B65AAFF407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -187,7 +187,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -201,6 +201,12 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F2329"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -223,9 +229,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -508,6 +515,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AA1048576"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="6" max="6" width="9.109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -4785,6 +4795,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
+      <c r="F91" s="2"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92">
@@ -6907,6 +6918,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
